--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44679</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>44285</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>44085</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>44679</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45595</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>45216</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44487</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45163</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44745</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45177</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>45176</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>45712</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45398</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44679</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44479</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44431</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>44848</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44537</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44278</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44938</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44531</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45411</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44597</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45294</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>44949</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>44949</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>45153</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44889</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45068</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45667.53913194445</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44930</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45236</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45140</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45176</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44308</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44104</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>45148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>45217</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>44496</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>45243</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>45695.55173611111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45293</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44088</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44082</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44411</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44077</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>44228</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44478</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44238</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44237</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>44201</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>44523</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44077</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>44420</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44608</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>44510</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44488</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>44420</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>44855</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>44095</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44573</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44846</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44411</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44564</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44496</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>44294</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44405</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>44405</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>44200</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44776</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44180</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44434</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>44221</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44466</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44419</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44085</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>44679</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>44679</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>44777</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44111</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44378</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44256</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44221</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44222</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44393</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>44350</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>44753</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44445</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44350</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44510</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44223</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44442</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44487</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44487</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44469</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44467</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44515</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>44342</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44405</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>44823</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44467</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44515</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>44449</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>44767</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44841</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>44537</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>44719</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44090</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44090</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44809</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>44378</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44057</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44884</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>44487</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44152</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>44356</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44253</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44223</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44628</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44319</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44497</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44378</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44378</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>44638</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>44826</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44791</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44515</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44848</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44803</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>44638</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44525</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44588</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44074</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44089</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>44627</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>44785</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>44643</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44116</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44147</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44087</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>44109</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>44595</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>44481</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>44574</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>44571</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>44812</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>44074</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>44796</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44393</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>44855</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>44110</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45302</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45746.70038194444</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>44090</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>44151</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>44151</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44412</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45364</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44916</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>45222</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>44930</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>45568</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45121</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>44862</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45245</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45359</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45275</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45275</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>44454</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>45140</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45308</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45111</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45492</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45379</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>45077</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45294</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>44565</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44588</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45090</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44442</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45217</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45217</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45429</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45177</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45374</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>44469</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>45082</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>44812</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44862</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45275</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>44768</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>44180</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45246</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44060</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45623</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45203</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45268</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>44865</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45153</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45568</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>44923</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44953</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>44933</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>44302</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44970</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>45316</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45741</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45265</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>44076</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>45219</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45082</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44085</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45271</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>44501</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>44475</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>44949</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45294</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45341</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45293</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>45342</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45300</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>44873</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45231</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>44929</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45639</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45670.86015046296</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45604</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45219</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45217</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>44894</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45655.82</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45275</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45489</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44936</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44931</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>44075</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>44881</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45208</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45618</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45111</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45775</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>44130</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44558</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44487</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45779.38840277777</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45779.36340277778</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45610</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45453</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45483</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44126.64</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44888</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44084</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>44509</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45120</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>44628</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>44937</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45741</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>44146</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45117</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>45785</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45140</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45125</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45116</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45470</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45342</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>44622</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45155</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45177</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45483</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>44099</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>45392</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45275</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45275</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>44608</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>44944</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45625</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45230</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>45202</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>45244</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>45244</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>44945</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>44643</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>44939</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>45140</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>45142</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>44229</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44803</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>45838</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>44859</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>45596</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>44600</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44795</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>44830</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>45230</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>45271</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44690</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>45071</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>44683</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>44933</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45089</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45804.44638888889</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45712</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45146</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34030,7 +34030,7 @@
         <v>44994</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>45614</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45244</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>44936</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>44967</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>45275</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34729,7 +34729,7 @@
         <v>45294</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45230</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45096</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45160</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>45141</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45225</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45142</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>44768</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>44909</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35614,7 +35614,7 @@
         <v>44342</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45205</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45596</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>44369</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45086</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36189,7 +36189,7 @@
         <v>45147</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>44293</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>44343</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>44767</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>44308</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45166</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
         <v>44768</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>44767</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>45769</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>44858</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>44413</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>44413</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>44089</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37867,7 +37867,7 @@
         <v>44930</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>44865</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45187</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44888</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44077</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45860</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>45275</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>45729</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45044</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>44930</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45821.43289351852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45309</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>45824</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>44509</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>45799</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44824</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>45827</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>45827</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>45293</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45013</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>45238</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>45729</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>45244</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45804</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44060</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44180</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44130</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45492</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44958</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>44810</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44221</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44945</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44949</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44208</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44641</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>44085</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>44097</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45071</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44459</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45147</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>45461</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44740</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44658</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45237</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44930</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45281</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44104</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>45049</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45146</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>44665</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45105</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>45236</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>44445</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>44767</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43355,7 +43355,7 @@
         <v>44931</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>44460</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44679</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>44285</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>44085</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>44679</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45595</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>45216</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44487</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45163</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44745</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45177</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>45176</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>45712</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45398</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44679</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44479</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44431</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>44848</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44537</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44278</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44938</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44531</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45411</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44597</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45294</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>44949</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>44949</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>45153</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44889</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45068</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45667.53913194445</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44930</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45236</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45140</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45176</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44308</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44104</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>45148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>45217</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>44496</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>45243</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>45695.55173611111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45293</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44088</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44082</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44411</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44077</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>44228</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44478</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44238</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44237</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>44201</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>44523</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44077</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>44420</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44608</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>44510</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44488</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>44420</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>44855</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>44095</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44573</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44846</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44411</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44564</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44496</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>44294</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44405</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>44405</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>44200</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44776</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44180</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44434</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>44221</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44466</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44419</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44085</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>44679</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>44679</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>44777</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44111</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44378</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44256</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44221</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44222</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44393</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>44350</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>44753</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44445</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44350</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44510</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44223</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44442</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44487</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44487</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44469</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>44467</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44515</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>44342</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44405</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>44823</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44467</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44515</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>44449</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>44767</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44841</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>44537</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>44719</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44090</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44090</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44809</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>44378</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44057</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44884</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>44487</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44152</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>44356</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44253</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44223</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44628</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44319</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44497</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44378</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44378</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>44638</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>44826</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44791</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44515</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44848</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44803</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>44638</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44525</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44588</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44074</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44089</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>44627</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>44785</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>44643</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44116</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44147</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44087</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>44109</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>44595</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>44481</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>44574</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>44571</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>44812</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>44074</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>44796</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44393</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>44855</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>44110</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45302</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45746.70038194444</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>44090</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>44151</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>44151</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44412</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45364</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44916</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>45222</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>44930</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>45568</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45121</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>44862</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45245</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45359</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45275</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45275</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>44454</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>45140</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45308</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45111</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45492</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45379</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>44159</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>45077</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45294</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>44565</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44588</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45090</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44442</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45217</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45217</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45429</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45177</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45374</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>44469</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>45082</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>44812</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44862</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>44412</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45275</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>44768</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>44180</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45246</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44060</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45623</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45203</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45268</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>44865</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45153</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45230</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45568</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>44923</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44953</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>44933</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>44302</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44970</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>45316</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45741</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45265</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>44076</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>45219</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45082</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44085</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45271</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>44501</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>44475</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>44949</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45294</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45341</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45293</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>45342</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45300</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>44873</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45231</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>44929</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45639</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45670.86015046296</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45604</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45219</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45217</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>44894</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45655.82</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45275</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45489</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44936</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44931</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>44075</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>44881</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45208</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45618</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45111</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45775</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>44130</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44558</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44487</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45779.38840277777</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45779.36340277778</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45610</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45453</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45483</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44126.64</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44888</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44084</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>44509</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45120</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>44628</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>44937</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45741</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>44146</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45117</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>45785</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45140</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45125</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45116</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45470</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45342</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>44622</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45155</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45177</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45483</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>44099</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>45392</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45275</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45275</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>44608</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>44944</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45625</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45230</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>45202</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>45244</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>45244</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>44945</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>44643</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>44939</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>45140</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>45142</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>44229</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44803</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>45838</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>44859</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>45596</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>44600</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44795</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>44830</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>45230</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>45271</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44690</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>45071</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>44683</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>44933</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45089</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45804.44638888889</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45712</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45146</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34030,7 +34030,7 @@
         <v>44994</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>45614</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45244</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>44936</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>44967</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>45275</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34729,7 +34729,7 @@
         <v>45294</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45230</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45096</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45160</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>45141</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45225</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45142</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>44768</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>44909</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35614,7 +35614,7 @@
         <v>44342</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45205</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45596</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>44369</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45086</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36189,7 +36189,7 @@
         <v>45147</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>44293</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>44343</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>44767</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>44308</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45166</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
         <v>44768</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>44767</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>45769</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>44858</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>44413</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>44413</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>44089</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37867,7 +37867,7 @@
         <v>44930</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>44865</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45187</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44888</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44077</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45860</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>45275</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>45729</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45044</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>44930</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45821.43289351852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45309</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>45824</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>44509</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>45799</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44824</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>45827</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>45827</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>45293</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45013</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>45238</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>45729</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>45244</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45804</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>44060</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44180</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44130</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45492</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44958</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>44810</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>44221</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44945</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44949</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44208</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44641</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>44085</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>44097</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45071</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44459</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45147</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>45461</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>44740</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>44658</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45237</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44930</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45281</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44104</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>45049</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45146</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>44665</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45105</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>45236</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>44445</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>44767</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43355,7 +43355,7 @@
         <v>44931</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>44460</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44679</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44285</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44085</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>44679</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45595</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45216</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45163</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44487</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45177</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>45176</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45712</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44745</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45398</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44479</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44431</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>44848</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>44537</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44278</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44679</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45236</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45140</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45176</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>44308</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>45148</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45243</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44930</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45293</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44104</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45217</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>44496</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45695.55173611111</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44088</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44938</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45294</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44531</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>44949</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>44949</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44597</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45068</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>45153</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44889</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>45667.53913194445</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44082</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44411</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>44077</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44228</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>44478</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>44238</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44237</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>44201</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44523</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44077</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>44608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44420</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>44510</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>44488</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44420</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44855</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44095</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44573</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44846</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44411</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44564</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44294</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44405</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44405</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44200</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44776</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44180</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>44466</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44434</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>44221</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>44085</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>44419</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44679</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44679</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44777</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44111</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>44378</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>44256</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>44221</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>44222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>44393</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>44350</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44753</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44445</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>44350</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44510</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>44223</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44442</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44487</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>44487</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>44469</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44467</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>44515</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44342</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>44405</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44823</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44515</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44449</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44767</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44090</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44719</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44090</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>44487</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44356</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>44628</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44253</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44319</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>44223</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>44378</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>44497</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>44378</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44638</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>44515</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>44826</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>44882</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>44791</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>44803</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>44848</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44525</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44638</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>44588</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>44074</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>44627</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>44089</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>44785</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44643</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44116</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44147</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44087</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44109</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44595</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44481</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>44574</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44571</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44074</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>44393</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>44812</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44796</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>44855</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44378</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44110</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44841</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44537</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44152</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44809</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>44090</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>44412</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>44884</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>44501</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>44949</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45294</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45341</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45379</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45639</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>45222</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45231</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>44442</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45670.86015046296</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45374</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45655.82</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44469</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45219</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45208</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45217</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45359</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45275</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45275</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45275</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>45775</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45489</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45111</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45779.38840277777</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45779.36340277778</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>44412</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>44558</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45453</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>45483</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>44509</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>45120</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44937</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45785</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45117</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45140</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45125</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45342</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>45116</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>45470</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45483</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44622</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45155</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45177</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44768</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45275</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45275</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44608</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45625</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>44643</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45804.44638888889</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>44803</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>44859</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>44600</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>44795</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>44060</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45268</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>44865</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45230</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>44933</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>44830</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45230</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>44970</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>45316</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>44076</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>45071</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>44683</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>44085</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>45271</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>44475</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>45293</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>45712</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45146</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>45342</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>44873</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44929</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45614</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>45604</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>45244</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>44894</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>45230</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44936</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>44931</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>44075</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>44881</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45160</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45618</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>44130</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>44487</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>45610</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44909</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>44126.64</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>44888</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>44084</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45205</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45860</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45821.43289351852</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45824</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44628</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>45799</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45741</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>44146</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>45166</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45827</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>45827</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44768</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>44767</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>45769</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>44858</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>44089</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>44930</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44865</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44888</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44077</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45275</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45729</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>45044</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>44930</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45309</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>45804</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>45838</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45293</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45238</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>45882.39939814815</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>45392</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>45244</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>44944</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>44060</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45230</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45202</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45244</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45244</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>44945</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>44939</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>44180</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45140</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45142</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44936</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>44229</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44130</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45492</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>44958</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>44810</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45596</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>44221</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44945</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>44942</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>45271</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>44949</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>44208</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44641</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44690</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44085</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44097</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44933</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>45089</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45071</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>44459</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>45147</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44994</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45461</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>44936</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>44967</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>44740</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>45275</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45294</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>44658</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45096</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35006,7 +35006,7 @@
         <v>45237</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44930</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45281</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>45141</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>45225</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45142</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>44768</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35829,7 +35829,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>44342</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>45596</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>44104</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>44369</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45086</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>45147</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>44293</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45049</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>44343</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>44767</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45146</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>44308</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>44665</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>45105</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>44413</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>44413</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45236</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>44445</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44767</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44931</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45187</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44460</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44509</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45302</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44824</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>45364</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44930</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45013</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45729</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45245</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45746.70038194444</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45140</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45308</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>44151</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>44151</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44916</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>45294</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>45568</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>45121</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45111</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>44862</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45217</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45217</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>44454</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>45429</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>45177</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45111</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45492</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>44159</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>45077</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>44565</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>44588</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>45090</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>45246</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>44123</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45082</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45623</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45203</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>44923</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>44953</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>44812</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>44862</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>44302</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45275</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45741</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45265</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>44180</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45219</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45082</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45153</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45568</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45300</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44679</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44285</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44085</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>44679</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45595</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45216</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45163</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44487</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45177</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>45176</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45712</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44745</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45398</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44479</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44431</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>44848</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>44537</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44278</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44679</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45236</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45140</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45176</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>44308</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>45148</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45243</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44930</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45293</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44104</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45217</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>44496</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45695.55173611111</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44088</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44938</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45294</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44531</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>44949</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>44949</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44597</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45068</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>45153</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44889</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>45667.53913194445</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44082</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44411</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>44077</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44228</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>44478</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>44238</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44237</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>44201</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44523</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44077</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>44608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44420</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>44510</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>44488</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44420</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44855</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44095</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44573</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44846</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44411</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44564</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44294</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44405</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44405</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44200</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44776</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44180</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>44466</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44434</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>44221</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>44085</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>44419</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44679</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44679</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44777</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44111</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>44378</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>44256</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>44221</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>44222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>44393</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>44350</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44753</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44445</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>44350</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44510</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>44223</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44442</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44487</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>44487</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>44469</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44467</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>44515</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44342</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>44405</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44823</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44515</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44449</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44767</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44090</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44719</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44090</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>44487</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44356</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>44628</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44253</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44319</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>44223</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>44378</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>44497</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>44378</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44638</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>44515</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>44826</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>44882</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>44791</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>44803</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>44848</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44525</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44638</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>44588</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>44074</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>44627</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>44089</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>44785</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44643</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44116</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44147</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44087</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44109</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44595</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44481</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>44574</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44571</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44074</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>44393</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>44812</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44796</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>44855</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>44378</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44110</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44841</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44537</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44152</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44809</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>44090</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>44412</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>44884</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>44501</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>44949</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45294</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45341</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45379</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45639</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>45222</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45231</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>44442</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45670.86015046296</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45374</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45655.82</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44469</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45219</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45208</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45217</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45359</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45275</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45275</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45275</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>45775</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45489</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45111</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45779.38840277777</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45779.36340277778</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>44412</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>44558</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45453</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>45483</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>44509</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>45120</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44937</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45785</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45117</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45140</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45125</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45342</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>45116</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>45470</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45483</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44622</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45155</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45177</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44099</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44768</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45275</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45275</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44608</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45625</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>44643</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45804.44638888889</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>44803</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>44859</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>44600</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>44795</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>44060</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45268</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>44865</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45230</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>44933</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>44830</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45230</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>44970</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>45316</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>44076</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>45071</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>44683</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>44085</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>45271</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>44475</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>45293</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>45712</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45146</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>45342</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>44873</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44929</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45614</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>45604</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>45244</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>44894</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>45230</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44936</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>44931</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>44075</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>44881</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45160</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45618</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>44130</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>44487</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>45610</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44909</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>44126.64</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>44888</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>44084</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45205</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45860</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45821.43289351852</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45824</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44628</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>45799</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45741</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>44146</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>45166</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45827</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>45827</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44768</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>44767</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>45769</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>44858</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>44089</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>44930</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44865</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44888</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44077</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45275</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45729</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>45044</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>44930</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45309</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>45804</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>45838</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45293</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45238</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>45882.39939814815</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>45392</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>45244</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>44944</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>44060</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45230</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45202</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45244</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45244</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>44945</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>44939</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>44180</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45140</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45142</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44936</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>44229</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44130</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45492</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>44958</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>44810</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45596</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>44221</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44945</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>44942</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>45271</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>44949</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>44208</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44641</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44690</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44085</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44097</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44933</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>45089</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45071</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>44459</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>45147</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44994</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45461</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>44936</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>44967</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>44740</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>45275</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45294</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>44658</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45096</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35006,7 +35006,7 @@
         <v>45237</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44930</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45281</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>45141</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>45225</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45142</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>44768</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35829,7 +35829,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>44342</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>45596</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>44104</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>44369</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45086</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>45147</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>44293</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45049</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>44343</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>44767</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45146</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>44308</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>44665</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>45105</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>44413</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>44413</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45236</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>44445</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>44767</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>44931</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45187</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>44460</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44509</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45302</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>44824</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>45364</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44930</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45013</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45729</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45245</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45746.70038194444</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45140</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45308</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>44151</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>44151</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44916</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>45294</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>45568</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>45121</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45111</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>44862</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45217</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45217</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>44454</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>45429</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>45177</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45111</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45492</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>44159</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>45077</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>44565</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>44588</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>45090</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>45246</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>44123</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45082</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45623</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45203</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>44923</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>44953</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>44812</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>44862</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>44302</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45275</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45741</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45265</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>44180</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45219</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45082</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45153</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45568</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45300</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44679</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44285</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>44085</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>44679</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45595</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45177</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>44745</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45216</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45398</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45712</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45163</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>44487</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45176</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44679</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44479</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44848</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>44431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44537</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44889</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44278</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>45236</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44938</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44930</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>45695.55173611111</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45294</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44496</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45176</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44088</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>44531</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>45243</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>44597</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44949</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44308</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45293</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>45667.53913194445</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44104</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>45217</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>45153</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>45148</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>45140</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>44949</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45068</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44082</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44411</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>44077</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44228</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>44478</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>44238</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44237</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>44201</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44523</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44077</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>44608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44420</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>44510</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>44488</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44420</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44855</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>44095</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44573</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>44846</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44411</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44564</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44294</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44405</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44405</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44200</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44776</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44466</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44221</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44085</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>44419</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>44180</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>44434</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44679</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44679</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44777</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44111</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>44378</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>44256</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>44221</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>44222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>44393</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>44350</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44753</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44445</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>44350</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44510</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>44223</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44442</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44487</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>44487</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>44467</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44469</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>44515</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44342</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>44405</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44823</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44515</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44449</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44767</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44719</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>44841</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44537</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>44090</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>44090</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>44809</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44378</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>44487</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>44152</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>44884</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44356</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>44223</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>44253</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44628</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>44319</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>44497</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>44378</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>44638</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>44826</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>44515</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>44791</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>44848</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44882</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>44525</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44803</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44638</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44074</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44588</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44627</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44785</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>44089</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>44643</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44116</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44595</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44087</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>44109</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>44481</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44147</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44074</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>44812</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44796</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44855</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44110</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44574</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>44571</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>44393</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>45089</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>45294</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>45236</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45219</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45746.70038194444</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45342</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>44967</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44767</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45364</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45177</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45275</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45275</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45275</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45140</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>44767</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45116</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>45146</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>45140</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>44862</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45470</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44810</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>44939</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>44308</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45187</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44930</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>45217</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>45217</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>45238</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45044</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>45300</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>45655.82</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>44622</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44812</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>44643</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45604</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45049</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45142</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45117</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45302</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45225</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>44090</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45105</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45618</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>44180</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45374</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44859</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45294</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45625</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45712</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45316</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44460</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44076</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45741</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45275</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45231</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>44949</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44768</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44930</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45268</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>44084</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44085</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>44159</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44293</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45779.36340277778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44909</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>44930</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>45275</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45785</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45153</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>45275</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45275</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45309</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45342</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>44097</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>45160</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>44658</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45217</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45141</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>44208</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>44445</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>44873</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>45096</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45483</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45071</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45741</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44894</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45246</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45271</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45177</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>44229</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>44123</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44454</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>44958</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>44077</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>44936</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45071</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>44085</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45453</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45293</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44442</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44343</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45222</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44683</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45146</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45245</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>44970</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>44888</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45308</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44487</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>45120</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45804.44638888889</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44608</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>44824</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45623</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>44949</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>44865</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>44413</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>44413</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>44180</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45013</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>44558</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45090</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>44937</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45111</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>45596</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44945</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>45077</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>45230</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45125</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45610</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>45492</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>44865</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44104</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>44469</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45729</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44130</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45359</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>44830</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>45208</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45147</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32560,7 +32560,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32617,7 +32617,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45147</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>44600</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32907,7 +32907,7 @@
         <v>45202</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>45155</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>45230</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45244</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33430,7 +33430,7 @@
         <v>45244</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45860</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>44099</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>44509</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>45799</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45341</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>45729</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44945</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>44302</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>45483</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>44130</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45824</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>44146</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>45281</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>45827</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>45827</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34895,7 +34895,7 @@
         <v>44916</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>44740</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35071,7 +35071,7 @@
         <v>44929</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>44933</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45082</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35413,7 +35413,7 @@
         <v>44768</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>44862</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45203</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45568</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45568</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>44930</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45492</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>45804</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>44665</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>45230</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>44475</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>44151</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>44151</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44953</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44126.64</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45379</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45142</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>44509</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>44936</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45271</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>44881</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>44795</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>44933</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>44942</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45293</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>44089</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>45082</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>45244</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45838</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>44858</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45275</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44412</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45639</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45882.39939814815</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>44342</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>44221</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>44936</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>44628</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>44931</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>45111</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>44412</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45489</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45614</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45887.71827546296</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>44369</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>44501</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>44931</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>45392</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>45775</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45889.68641203704</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45888</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45219</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>44994</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45294</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41198,7 +41198,7 @@
         <v>44944</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41374,7 +41374,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>45244</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>45205</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44641</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45121</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45461</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45237</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45140</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45111</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>44767</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45230</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>44588</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45265</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>44803</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>45086</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>44075</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>45429</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42871,7 +42871,7 @@
         <v>44459</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>44565</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>44690</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>44768</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>44888</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44679</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1646,14 +1646,14 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 40469-2024</t>
+          <t>A 9192-2025</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>45555.53145833333</v>
+        <v>45714.45943287037</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>24.5</v>
+        <v>17.4</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1695,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1704,6 +1704,99 @@
         <v>4</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Purpurknipprot
+Svart jordtunga
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="S13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0580/artfynd/A 9192-2025 artfynd.xlsx", "A 9192-2025")</f>
+        <v/>
+      </c>
+      <c r="T13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0580/kartor/A 9192-2025 karta.png", "A 9192-2025")</f>
+        <v/>
+      </c>
+      <c r="V13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomål/A 9192-2025 FSC-klagomål.docx", "A 9192-2025")</f>
+        <v/>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomålsmail/A 9192-2025 FSC-klagomål mail.docx", "A 9192-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsyn/A 9192-2025 tillsynsbegäran.docx", "A 9192-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsynsmail/A 9192-2025 tillsynsbegäran mail.docx", "A 9192-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 40469-2024</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>45555.53145833333</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LINKÖPING</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>Brunpudrad nållav
 Brandticka
@@ -1711,92 +1804,92 @@
 Kornig nållav</t>
         </is>
       </c>
-      <c r="S13">
+      <c r="S14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/artfynd/A 40469-2024 artfynd.xlsx", "A 40469-2024")</f>
         <v/>
       </c>
-      <c r="T13">
+      <c r="T14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/kartor/A 40469-2024 karta.png", "A 40469-2024")</f>
         <v/>
       </c>
-      <c r="V13">
+      <c r="V14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomål/A 40469-2024 FSC-klagomål.docx", "A 40469-2024")</f>
         <v/>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomålsmail/A 40469-2024 FSC-klagomål mail.docx", "A 40469-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsyn/A 40469-2024 tillsynsbegäran.docx", "A 40469-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsynsmail/A 40469-2024 tillsynsbegäran mail.docx", "A 40469-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 15475-2021</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B15" s="1" t="n">
         <v>44285</v>
       </c>
-      <c r="C14" s="1" t="n">
-        <v>45893</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>LINKÖPING</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="C15" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LINKÖPING</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="G15" t="n">
         <v>10.2</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H15" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>4</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P15" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q15" t="n">
         <v>4</v>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Grönsångare
@@ -1804,389 +1897,297 @@
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="S14">
+      <c r="S15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/artfynd/A 15475-2021 artfynd.xlsx", "A 15475-2021")</f>
         <v/>
       </c>
-      <c r="T14">
+      <c r="T15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/kartor/A 15475-2021 karta.png", "A 15475-2021")</f>
         <v/>
       </c>
-      <c r="V14">
+      <c r="V15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomål/A 15475-2021 FSC-klagomål.docx", "A 15475-2021")</f>
         <v/>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomålsmail/A 15475-2021 FSC-klagomål mail.docx", "A 15475-2021")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsyn/A 15475-2021 tillsynsbegäran.docx", "A 15475-2021")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsynsmail/A 15475-2021 tillsynsbegäran mail.docx", "A 15475-2021")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="Z15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/fåglar/A 15475-2021 prioriterade fågelarter.docx", "A 15475-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 55341-2024</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B16" s="1" t="n">
         <v>45621.71255787037</v>
       </c>
-      <c r="C15" s="1" t="n">
-        <v>45893</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LINKÖPING</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+      <c r="C16" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LINKÖPING</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>4.3</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P16" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q16" t="n">
         <v>3</v>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Rynkskinn
 Barkticka
 Smal svampklubba</t>
         </is>
       </c>
-      <c r="S15">
+      <c r="S16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/artfynd/A 55341-2024 artfynd.xlsx", "A 55341-2024")</f>
         <v/>
       </c>
-      <c r="T15">
+      <c r="T16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/kartor/A 55341-2024 karta.png", "A 55341-2024")</f>
         <v/>
       </c>
-      <c r="V15">
+      <c r="V16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomål/A 55341-2024 FSC-klagomål.docx", "A 55341-2024")</f>
         <v/>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomålsmail/A 55341-2024 FSC-klagomål mail.docx", "A 55341-2024")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsyn/A 55341-2024 tillsynsbegäran.docx", "A 55341-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsynsmail/A 55341-2024 tillsynsbegäran mail.docx", "A 55341-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 577-2025</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B17" s="1" t="n">
         <v>45664.56525462963</v>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>45893</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LINKÖPING</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+      <c r="C17" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LINKÖPING</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>3.7</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H17" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Dvärgpipistrell
 Större brunfladdermus</t>
         </is>
       </c>
-      <c r="S16">
+      <c r="S17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/artfynd/A 577-2025 artfynd.xlsx", "A 577-2025")</f>
         <v/>
       </c>
-      <c r="T16">
+      <c r="T17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/kartor/A 577-2025 karta.png", "A 577-2025")</f>
         <v/>
       </c>
-      <c r="V16">
+      <c r="V17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomål/A 577-2025 FSC-klagomål.docx", "A 577-2025")</f>
         <v/>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomålsmail/A 577-2025 FSC-klagomål mail.docx", "A 577-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsyn/A 577-2025 tillsynsbegäran.docx", "A 577-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsynsmail/A 577-2025 tillsynsbegäran mail.docx", "A 577-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 17275-2025</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B18" s="1" t="n">
         <v>45756.55734953703</v>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>45893</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LINKÖPING</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
+      <c r="C18" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LINKÖPING</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>2.9</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>3</v>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Fällmossa
 Platt fjädermossa</t>
         </is>
       </c>
-      <c r="S17">
+      <c r="S18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/artfynd/A 17275-2025 artfynd.xlsx", "A 17275-2025")</f>
         <v/>
       </c>
-      <c r="T17">
+      <c r="T18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/kartor/A 17275-2025 karta.png", "A 17275-2025")</f>
         <v/>
       </c>
-      <c r="V17">
+      <c r="V18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomål/A 17275-2025 FSC-klagomål.docx", "A 17275-2025")</f>
         <v/>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomålsmail/A 17275-2025 FSC-klagomål mail.docx", "A 17275-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsyn/A 17275-2025 tillsynsbegäran.docx", "A 17275-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsynsmail/A 17275-2025 tillsynsbegäran mail.docx", "A 17275-2025")</f>
         <v/>
       </c>
-      <c r="Z17">
+      <c r="Z18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0580/fåglar/A 17275-2025 prioriterade fågelarter.docx", "A 17275-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 9192-2025</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>45714.45943287037</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>45893</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LINKÖPING</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>Purpurknipprot
-Svart jordtunga
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="S18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0580/artfynd/A 9192-2025 artfynd.xlsx", "A 9192-2025")</f>
-        <v/>
-      </c>
-      <c r="T18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0580/kartor/A 9192-2025 karta.png", "A 9192-2025")</f>
-        <v/>
-      </c>
-      <c r="V18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomål/A 9192-2025 FSC-klagomål.docx", "A 9192-2025")</f>
-        <v/>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0580/klagomålsmail/A 9192-2025 FSC-klagomål mail.docx", "A 9192-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsyn/A 9192-2025 tillsynsbegäran.docx", "A 9192-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0580/tillsynsmail/A 9192-2025 tillsynsbegäran mail.docx", "A 9192-2025")</f>
         <v/>
       </c>
     </row>
@@ -2200,7 +2201,7 @@
         <v>44085</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2287,7 +2288,7 @@
         <v>44679</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2379,7 @@
         <v>45595</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2465,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2550,7 +2551,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2640,7 +2641,7 @@
         <v>45177</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2726,7 +2727,7 @@
         <v>44745</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2813,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2898,7 +2899,7 @@
         <v>45216</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2984,7 +2985,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3070,7 +3071,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3156,7 +3157,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3242,7 +3243,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3332,7 +3333,7 @@
         <v>45398</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3423,7 +3424,7 @@
         <v>45712</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3514,7 +3515,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3600,7 +3601,7 @@
         <v>45163</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3686,7 +3687,7 @@
         <v>44487</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3778,7 @@
         <v>45176</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3863,7 +3864,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3952,7 +3953,7 @@
         <v>44679</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4042,7 +4043,7 @@
         <v>44479</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4133,7 @@
         <v>44848</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4217,7 +4218,7 @@
         <v>44431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4302,7 +4303,7 @@
         <v>44537</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4393,7 @@
         <v>44889</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4477,7 +4478,7 @@
         <v>44278</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4562,7 +4563,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4652,7 +4653,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4742,7 +4743,7 @@
         <v>45236</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4832,7 @@
         <v>44938</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4916,7 +4917,7 @@
         <v>44930</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5006,7 +5007,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5096,7 +5097,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5181,7 +5182,7 @@
         <v>45695.55173611111</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5271,7 +5272,7 @@
         <v>45294</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5356,7 +5357,7 @@
         <v>44496</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5446,7 +5447,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5531,7 +5532,7 @@
         <v>45176</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5616,7 +5617,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5701,7 +5702,7 @@
         <v>44088</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5790,7 +5791,7 @@
         <v>44531</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5880,7 +5881,7 @@
         <v>45243</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5970,7 +5971,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6055,7 +6056,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6140,7 +6141,7 @@
         <v>44597</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6225,7 +6226,7 @@
         <v>44949</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6310,7 +6311,7 @@
         <v>44308</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6395,7 +6396,7 @@
         <v>45293</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6480,7 +6481,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6570,7 +6571,7 @@
         <v>45667.53913194445</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6655,7 +6656,7 @@
         <v>44104</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6740,7 +6741,7 @@
         <v>45217</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6830,7 +6831,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6919,7 +6920,7 @@
         <v>45153</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7009,7 +7010,7 @@
         <v>45148</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7094,7 +7095,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7179,7 +7180,7 @@
         <v>45140</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7268,7 +7269,7 @@
         <v>44949</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7353,7 +7354,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7438,7 +7439,7 @@
         <v>45068</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7528,7 +7529,7 @@
         <v>44082</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7585,7 +7586,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7642,7 +7643,7 @@
         <v>44411</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7699,7 +7700,7 @@
         <v>44077</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7756,7 +7757,7 @@
         <v>44228</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7818,7 +7819,7 @@
         <v>44478</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7880,7 +7881,7 @@
         <v>44238</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7937,7 +7938,7 @@
         <v>44237</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7994,7 +7995,7 @@
         <v>44201</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8051,7 +8052,7 @@
         <v>44523</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8108,7 +8109,7 @@
         <v>44077</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8165,7 +8166,7 @@
         <v>44608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8222,7 +8223,7 @@
         <v>44420</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8279,7 +8280,7 @@
         <v>44510</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8336,7 +8337,7 @@
         <v>44488</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8393,7 +8394,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8450,7 +8451,7 @@
         <v>44420</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8507,7 +8508,7 @@
         <v>44855</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8569,7 +8570,7 @@
         <v>44095</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8631,7 +8632,7 @@
         <v>44573</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8688,7 +8689,7 @@
         <v>44846</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8745,7 +8746,7 @@
         <v>44411</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8802,7 +8803,7 @@
         <v>44564</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8859,7 +8860,7 @@
         <v>44496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8916,7 +8917,7 @@
         <v>44294</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8973,7 +8974,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9030,7 +9031,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9087,7 +9088,7 @@
         <v>44405</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9144,7 +9145,7 @@
         <v>44405</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9201,7 +9202,7 @@
         <v>44200</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9258,7 +9259,7 @@
         <v>44776</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9315,7 +9316,7 @@
         <v>44466</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9372,7 +9373,7 @@
         <v>44221</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9434,7 +9435,7 @@
         <v>44085</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9491,7 +9492,7 @@
         <v>44419</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9548,7 +9549,7 @@
         <v>44180</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9610,7 +9611,7 @@
         <v>44434</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9672,7 +9673,7 @@
         <v>44679</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9734,7 +9735,7 @@
         <v>44679</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9796,7 +9797,7 @@
         <v>44777</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9853,7 +9854,7 @@
         <v>44111</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9910,7 +9911,7 @@
         <v>44378</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9967,7 +9968,7 @@
         <v>44256</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10029,7 +10030,7 @@
         <v>44221</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10086,7 +10087,7 @@
         <v>44222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10143,7 +10144,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10200,7 +10201,7 @@
         <v>44393</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10262,7 +10263,7 @@
         <v>44350</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10324,7 +10325,7 @@
         <v>44753</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10386,7 +10387,7 @@
         <v>44445</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10448,7 +10449,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10505,7 +10506,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10567,7 +10568,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10624,7 +10625,7 @@
         <v>44350</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10681,7 +10682,7 @@
         <v>44510</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10738,7 +10739,7 @@
         <v>44223</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10795,7 +10796,7 @@
         <v>44442</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10852,7 +10853,7 @@
         <v>44487</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10914,7 +10915,7 @@
         <v>44487</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10976,7 +10977,7 @@
         <v>44467</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11033,7 +11034,7 @@
         <v>44469</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11090,7 +11091,7 @@
         <v>44515</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11152,7 +11153,7 @@
         <v>44342</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11214,7 +11215,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11271,7 +11272,7 @@
         <v>44405</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11328,7 +11329,7 @@
         <v>44823</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11385,7 +11386,7 @@
         <v>44467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11442,7 +11443,7 @@
         <v>44515</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11504,7 +11505,7 @@
         <v>44449</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11561,7 +11562,7 @@
         <v>44767</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11618,7 +11619,7 @@
         <v>44719</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11680,7 +11681,7 @@
         <v>44841</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11737,7 +11738,7 @@
         <v>44537</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11794,7 +11795,7 @@
         <v>44090</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11851,7 +11852,7 @@
         <v>44090</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11908,7 +11909,7 @@
         <v>44809</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11965,7 +11966,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12022,7 +12023,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12079,7 +12080,7 @@
         <v>44378</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12136,7 +12137,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12193,7 +12194,7 @@
         <v>44487</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12255,7 +12256,7 @@
         <v>44152</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12317,7 +12318,7 @@
         <v>44884</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12374,7 +12375,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12431,7 +12432,7 @@
         <v>44356</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12488,7 +12489,7 @@
         <v>44223</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12545,7 +12546,7 @@
         <v>44253</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12602,7 +12603,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12659,7 +12660,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12716,7 +12717,7 @@
         <v>44628</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12773,7 +12774,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12830,7 +12831,7 @@
         <v>44319</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12887,7 +12888,7 @@
         <v>44497</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12944,7 +12945,7 @@
         <v>44378</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13001,7 +13002,7 @@
         <v>44638</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13058,7 +13059,7 @@
         <v>44826</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13115,7 +13116,7 @@
         <v>44515</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13177,7 +13178,7 @@
         <v>44791</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13234,7 +13235,7 @@
         <v>44848</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13291,7 +13292,7 @@
         <v>44882</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13353,7 +13354,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13410,7 +13411,7 @@
         <v>44525</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13467,7 +13468,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13524,7 +13525,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13581,7 +13582,7 @@
         <v>44803</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13638,7 +13639,7 @@
         <v>44638</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13695,7 +13696,7 @@
         <v>44074</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13757,7 +13758,7 @@
         <v>44588</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13814,7 +13815,7 @@
         <v>44627</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13871,7 +13872,7 @@
         <v>44785</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13928,7 +13929,7 @@
         <v>44089</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13985,7 +13986,7 @@
         <v>44643</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14042,7 +14043,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14099,7 +14100,7 @@
         <v>44116</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14156,7 +14157,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14213,7 +14214,7 @@
         <v>44595</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14275,7 +14276,7 @@
         <v>44087</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14337,7 +14338,7 @@
         <v>44109</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14394,7 +14395,7 @@
         <v>44481</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14451,7 +14452,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14508,7 +14509,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14570,7 +14571,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14632,7 +14633,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14689,7 +14690,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14746,7 +14747,7 @@
         <v>44147</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14803,7 +14804,7 @@
         <v>44074</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14865,7 +14866,7 @@
         <v>44812</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14922,7 +14923,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14979,7 +14980,7 @@
         <v>44796</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15041,7 +15042,7 @@
         <v>44855</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15098,7 +15099,7 @@
         <v>44110</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15155,7 +15156,7 @@
         <v>44574</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15212,7 +15213,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15269,7 +15270,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15326,7 +15327,7 @@
         <v>44571</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15383,7 +15384,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15440,7 +15441,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15497,7 +15498,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15554,7 +15555,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15616,7 +15617,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15673,7 +15674,7 @@
         <v>44393</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15735,7 +15736,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15792,7 +15793,7 @@
         <v>45089</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15854,7 +15855,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15911,7 +15912,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15973,7 +15974,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16030,7 +16031,7 @@
         <v>45294</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16087,7 +16088,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16144,7 +16145,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16201,7 +16202,7 @@
         <v>45236</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16263,7 +16264,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16320,7 +16321,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16377,7 +16378,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16439,7 +16440,7 @@
         <v>45219</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16501,7 +16502,7 @@
         <v>45746.70038194444</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16558,7 +16559,7 @@
         <v>45342</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16615,7 +16616,7 @@
         <v>44967</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16677,7 +16678,7 @@
         <v>44767</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16734,7 +16735,7 @@
         <v>45364</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16796,7 +16797,7 @@
         <v>45177</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16853,7 +16854,7 @@
         <v>45275</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16910,7 +16911,7 @@
         <v>45275</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16972,7 +16973,7 @@
         <v>45275</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17029,7 +17030,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17091,7 +17092,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17148,7 +17149,7 @@
         <v>45140</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17205,7 +17206,7 @@
         <v>44767</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17262,7 +17263,7 @@
         <v>45116</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17319,7 +17320,7 @@
         <v>45146</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17381,7 +17382,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17443,7 +17444,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17505,7 +17506,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17562,7 +17563,7 @@
         <v>45140</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17619,7 +17620,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17676,7 +17677,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17733,7 +17734,7 @@
         <v>44862</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17790,7 +17791,7 @@
         <v>45470</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17852,7 +17853,7 @@
         <v>44810</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17909,7 +17910,7 @@
         <v>44939</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17966,7 +17967,7 @@
         <v>44308</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18028,7 +18029,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18085,7 +18086,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18142,7 +18143,7 @@
         <v>45187</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18204,7 +18205,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18266,7 +18267,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18328,7 +18329,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18390,7 +18391,7 @@
         <v>44930</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18452,7 +18453,7 @@
         <v>45217</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18509,7 +18510,7 @@
         <v>45217</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18566,7 +18567,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18623,7 +18624,7 @@
         <v>45238</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18680,7 +18681,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18737,7 +18738,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18794,7 +18795,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18851,7 +18852,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18908,7 +18909,7 @@
         <v>45044</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18965,7 +18966,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19022,7 +19023,7 @@
         <v>45300</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19084,7 +19085,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19141,7 +19142,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19198,7 +19199,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19260,7 +19261,7 @@
         <v>45655.82</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19317,7 +19318,7 @@
         <v>44622</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19374,7 +19375,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19431,7 +19432,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19488,7 +19489,7 @@
         <v>44812</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19545,7 +19546,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19602,7 +19603,7 @@
         <v>44643</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19659,7 +19660,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19716,7 +19717,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19773,7 +19774,7 @@
         <v>45604</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19835,7 +19836,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19892,7 +19893,7 @@
         <v>45049</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19949,7 +19950,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20006,7 +20007,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20063,7 +20064,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20120,7 +20121,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20177,7 +20178,7 @@
         <v>45142</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20234,7 +20235,7 @@
         <v>45117</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20291,7 +20292,7 @@
         <v>45302</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20348,7 +20349,7 @@
         <v>45225</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20410,7 +20411,7 @@
         <v>44090</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20467,7 +20468,7 @@
         <v>45105</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20529,7 +20530,7 @@
         <v>45618</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20586,7 +20587,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20643,7 +20644,7 @@
         <v>44180</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20705,7 +20706,7 @@
         <v>45374</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20762,7 +20763,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20824,7 +20825,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20881,7 +20882,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20938,7 +20939,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20995,7 +20996,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21052,7 +21053,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21109,7 +21110,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21171,7 +21172,7 @@
         <v>44859</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21233,7 +21234,7 @@
         <v>45294</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21295,7 +21296,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21352,7 +21353,7 @@
         <v>45625</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21409,7 +21410,7 @@
         <v>45712</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21466,7 +21467,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21523,7 +21524,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21580,7 +21581,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21637,7 +21638,7 @@
         <v>45316</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21694,7 +21695,7 @@
         <v>44460</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21751,7 +21752,7 @@
         <v>44076</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21808,7 +21809,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21865,7 +21866,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21922,7 +21923,7 @@
         <v>45741</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21979,7 +21980,7 @@
         <v>45275</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22036,7 +22037,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22098,7 +22099,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22155,7 +22156,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22212,7 +22213,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22274,7 +22275,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22331,7 +22332,7 @@
         <v>45231</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22388,7 +22389,7 @@
         <v>44949</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22445,7 +22446,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22502,7 +22503,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22559,7 +22560,7 @@
         <v>44768</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22616,7 +22617,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22673,7 +22674,7 @@
         <v>44930</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22735,7 +22736,7 @@
         <v>45268</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22792,7 +22793,7 @@
         <v>44084</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22849,7 +22850,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22906,7 +22907,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22963,7 +22964,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23020,7 +23021,7 @@
         <v>44085</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23082,7 +23083,7 @@
         <v>44159</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23139,7 +23140,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23196,7 +23197,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23253,7 +23254,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23310,7 +23311,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23367,7 +23368,7 @@
         <v>44293</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23429,7 +23430,7 @@
         <v>45779.36340277778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23486,7 +23487,7 @@
         <v>44909</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23543,7 +23544,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23600,7 +23601,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23657,7 +23658,7 @@
         <v>44930</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23719,7 +23720,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23776,7 +23777,7 @@
         <v>45275</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23833,7 +23834,7 @@
         <v>45785</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23890,7 +23891,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23947,7 +23948,7 @@
         <v>45153</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24009,7 +24010,7 @@
         <v>45275</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24071,7 +24072,7 @@
         <v>45275</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24133,7 +24134,7 @@
         <v>45309</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24190,7 +24191,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24247,7 +24248,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24304,7 +24305,7 @@
         <v>45342</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24361,7 +24362,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24418,7 +24419,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24475,7 +24476,7 @@
         <v>44097</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24532,7 +24533,7 @@
         <v>45160</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24589,7 +24590,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24646,7 +24647,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24703,7 +24704,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24760,7 +24761,7 @@
         <v>44658</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24817,7 +24818,7 @@
         <v>45217</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24874,7 +24875,7 @@
         <v>45141</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24931,7 +24932,7 @@
         <v>44208</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24988,7 +24989,7 @@
         <v>44445</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25050,7 +25051,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25107,7 +25108,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25164,7 +25165,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25221,7 +25222,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25278,7 +25279,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25335,7 +25336,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25392,7 +25393,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25449,7 +25450,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25506,7 +25507,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25563,7 +25564,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25620,7 +25621,7 @@
         <v>44873</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25682,7 +25683,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25739,7 +25740,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25796,7 +25797,7 @@
         <v>45096</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25858,7 +25859,7 @@
         <v>45483</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25915,7 +25916,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25972,7 +25973,7 @@
         <v>45071</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26034,7 +26035,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26091,7 +26092,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26148,7 +26149,7 @@
         <v>45741</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26205,7 +26206,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26262,7 +26263,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26319,7 +26320,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26376,7 +26377,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26433,7 +26434,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26495,7 +26496,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26552,7 +26553,7 @@
         <v>44894</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26609,7 +26610,7 @@
         <v>45246</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26671,7 +26672,7 @@
         <v>45271</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26728,7 +26729,7 @@
         <v>45177</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26785,7 +26786,7 @@
         <v>44229</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26842,7 +26843,7 @@
         <v>44123</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26899,7 +26900,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26956,7 +26957,7 @@
         <v>44454</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27013,7 +27014,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27070,7 +27071,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27127,7 +27128,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27184,7 +27185,7 @@
         <v>44958</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27241,7 +27242,7 @@
         <v>44077</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27298,7 +27299,7 @@
         <v>44936</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27355,7 +27356,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27412,7 +27413,7 @@
         <v>45071</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27474,7 +27475,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27531,7 +27532,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27588,7 +27589,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27650,7 +27651,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27707,7 +27708,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27764,7 +27765,7 @@
         <v>44085</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27821,7 +27822,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27878,7 +27879,7 @@
         <v>45453</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27935,7 +27936,7 @@
         <v>45293</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27992,7 +27993,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28049,7 +28050,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28106,7 +28107,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28163,7 +28164,7 @@
         <v>44442</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28220,7 +28221,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28277,7 +28278,7 @@
         <v>44343</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28334,7 +28335,7 @@
         <v>45222</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28396,7 +28397,7 @@
         <v>44683</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28453,7 +28454,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28510,7 +28511,7 @@
         <v>45146</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28572,7 +28573,7 @@
         <v>45245</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28634,7 +28635,7 @@
         <v>44970</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28696,7 +28697,7 @@
         <v>44888</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28753,7 +28754,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28810,7 +28811,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28867,7 +28868,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28924,7 +28925,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28981,7 +28982,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29038,7 +29039,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29095,7 +29096,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29152,7 +29153,7 @@
         <v>45308</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29214,7 +29215,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29271,7 +29272,7 @@
         <v>44487</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29333,7 +29334,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29390,7 +29391,7 @@
         <v>45120</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29447,7 +29448,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29509,7 +29510,7 @@
         <v>45804.44638888889</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29566,7 +29567,7 @@
         <v>44608</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29628,7 +29629,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29685,7 +29686,7 @@
         <v>44824</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29742,7 +29743,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29799,7 +29800,7 @@
         <v>45623</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29856,7 +29857,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29913,7 +29914,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29970,7 +29971,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30027,7 +30028,7 @@
         <v>44949</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30084,7 +30085,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30141,7 +30142,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30203,7 +30204,7 @@
         <v>44865</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30265,7 +30266,7 @@
         <v>44413</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30322,7 +30323,7 @@
         <v>44413</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30379,7 +30380,7 @@
         <v>44180</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30441,7 +30442,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30498,7 +30499,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30555,7 +30556,7 @@
         <v>45013</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30612,7 +30613,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30669,7 +30670,7 @@
         <v>44558</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30726,7 +30727,7 @@
         <v>45090</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30783,7 +30784,7 @@
         <v>44937</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30840,7 +30841,7 @@
         <v>45111</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30902,7 +30903,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30959,7 +30960,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31016,7 +31017,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31073,7 +31074,7 @@
         <v>45596</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31130,7 +31131,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31187,7 +31188,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31244,7 +31245,7 @@
         <v>44945</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31301,7 +31302,7 @@
         <v>45077</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31358,7 +31359,7 @@
         <v>45230</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31415,7 +31416,7 @@
         <v>45125</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31472,7 +31473,7 @@
         <v>45610</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31529,7 +31530,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31586,7 +31587,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31643,7 +31644,7 @@
         <v>45492</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31700,7 +31701,7 @@
         <v>44865</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31757,7 +31758,7 @@
         <v>44104</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31814,7 +31815,7 @@
         <v>44469</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31871,7 +31872,7 @@
         <v>45729</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31933,7 +31934,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31990,7 +31991,7 @@
         <v>44130</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32047,7 +32048,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32104,7 +32105,7 @@
         <v>45359</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32161,7 +32162,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32218,7 +32219,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32275,7 +32276,7 @@
         <v>44830</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32332,7 +32333,7 @@
         <v>45208</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32389,7 +32390,7 @@
         <v>45147</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32446,7 +32447,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32503,7 +32504,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32560,7 +32561,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32617,7 +32618,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32674,7 +32675,7 @@
         <v>45147</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32731,7 +32732,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32788,7 +32789,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32850,7 +32851,7 @@
         <v>44600</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32907,7 +32908,7 @@
         <v>45202</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32964,7 +32965,7 @@
         <v>45155</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33021,7 +33022,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33078,7 +33079,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33135,7 +33136,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33197,7 +33198,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33254,7 +33255,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33311,7 +33312,7 @@
         <v>45230</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33368,7 +33369,7 @@
         <v>45244</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33430,7 +33431,7 @@
         <v>45244</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33492,7 +33493,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33549,7 +33550,7 @@
         <v>45860</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33606,7 +33607,7 @@
         <v>44099</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33663,7 +33664,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33720,7 +33721,7 @@
         <v>44509</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33782,7 +33783,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33844,7 +33845,7 @@
         <v>45799</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33901,7 +33902,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33963,7 +33964,7 @@
         <v>45341</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34020,7 +34021,7 @@
         <v>45729</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34077,7 +34078,7 @@
         <v>44945</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34134,7 +34135,7 @@
         <v>44302</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34191,7 +34192,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34248,7 +34249,7 @@
         <v>45483</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34305,7 +34306,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34362,7 +34363,7 @@
         <v>44130</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34419,7 +34420,7 @@
         <v>45824</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34476,7 +34477,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34533,7 +34534,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34595,7 +34596,7 @@
         <v>44146</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34652,7 +34653,7 @@
         <v>45281</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34714,7 +34715,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34771,7 +34772,7 @@
         <v>45827</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34833,7 +34834,7 @@
         <v>45827</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34895,7 +34896,7 @@
         <v>44916</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34957,7 +34958,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35014,7 +35015,7 @@
         <v>44740</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35071,7 +35072,7 @@
         <v>44929</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35128,7 +35129,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35185,7 +35186,7 @@
         <v>44933</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35242,7 +35243,7 @@
         <v>45082</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35299,7 +35300,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35356,7 +35357,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35413,7 +35414,7 @@
         <v>44768</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35470,7 +35471,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35527,7 +35528,7 @@
         <v>44862</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35584,7 +35585,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35646,7 +35647,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35708,7 +35709,7 @@
         <v>45203</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35765,7 +35766,7 @@
         <v>45568</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35822,7 +35823,7 @@
         <v>45568</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35879,7 +35880,7 @@
         <v>44930</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35941,7 +35942,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35998,7 +35999,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36055,7 +36056,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36112,7 +36113,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36169,7 +36170,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36226,7 +36227,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36283,7 +36284,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36340,7 +36341,7 @@
         <v>45492</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36397,7 +36398,7 @@
         <v>45804</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36454,7 +36455,7 @@
         <v>44665</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36516,7 +36517,7 @@
         <v>45230</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36573,7 +36574,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36630,7 +36631,7 @@
         <v>44475</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36687,7 +36688,7 @@
         <v>44151</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36744,7 +36745,7 @@
         <v>44151</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36801,7 +36802,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36858,7 +36859,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36915,7 +36916,7 @@
         <v>44953</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36972,7 +36973,7 @@
         <v>44126.64</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37029,7 +37030,7 @@
         <v>45379</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37086,7 +37087,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37143,7 +37144,7 @@
         <v>45142</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37200,7 +37201,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37262,7 +37263,7 @@
         <v>44509</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37319,7 +37320,7 @@
         <v>44936</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37376,7 +37377,7 @@
         <v>45271</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37433,7 +37434,7 @@
         <v>44881</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37490,7 +37491,7 @@
         <v>44795</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37547,7 +37548,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37604,7 +37605,7 @@
         <v>44933</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37661,7 +37662,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37718,7 +37719,7 @@
         <v>44942</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37775,7 +37776,7 @@
         <v>45293</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37832,7 +37833,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37889,7 +37890,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37946,7 +37947,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38008,7 +38009,7 @@
         <v>44089</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38065,7 +38066,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38122,7 +38123,7 @@
         <v>45082</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38179,7 +38180,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38236,7 +38237,7 @@
         <v>45244</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38298,7 +38299,7 @@
         <v>45838</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38355,7 +38356,7 @@
         <v>44858</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38412,7 +38413,7 @@
         <v>45275</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38474,7 +38475,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38531,7 +38532,7 @@
         <v>44412</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38593,7 +38594,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38650,7 +38651,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38707,7 +38708,7 @@
         <v>45639</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38764,7 +38765,7 @@
         <v>45882.39939814815</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38821,7 +38822,7 @@
         <v>44342</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38883,7 +38884,7 @@
         <v>44221</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38940,7 +38941,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38997,7 +38998,7 @@
         <v>44936</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39054,7 +39055,7 @@
         <v>44628</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39111,7 +39112,7 @@
         <v>44931</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39168,7 +39169,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39225,7 +39226,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39282,7 +39283,7 @@
         <v>45111</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39344,7 +39345,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39401,7 +39402,7 @@
         <v>44412</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39458,7 +39459,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39520,7 +39521,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39577,7 +39578,7 @@
         <v>45489</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39634,7 +39635,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39691,7 +39692,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39748,7 +39749,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39805,7 +39806,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39867,7 +39868,7 @@
         <v>45614</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39924,7 +39925,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39981,7 +39982,7 @@
         <v>45887.71827546296</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40038,7 +40039,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40095,7 +40096,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40152,7 +40153,7 @@
         <v>44369</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40209,7 +40210,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40266,7 +40267,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40323,7 +40324,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40380,7 +40381,7 @@
         <v>44501</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40437,7 +40438,7 @@
         <v>44931</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40494,7 +40495,7 @@
         <v>45392</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40551,7 +40552,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40613,7 +40614,7 @@
         <v>45775</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40675,7 +40676,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40732,7 +40733,7 @@
         <v>45889.68641203704</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40789,7 +40790,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40846,7 +40847,7 @@
         <v>45888</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40903,7 +40904,7 @@
         <v>45219</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40965,7 +40966,7 @@
         <v>44994</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41022,7 +41023,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41079,7 +41080,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41136,7 +41137,7 @@
         <v>45294</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41198,7 +41199,7 @@
         <v>44944</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41255,7 +41256,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41317,7 +41318,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41374,7 +41375,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41431,7 +41432,7 @@
         <v>45244</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41493,7 +41494,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41550,7 +41551,7 @@
         <v>45205</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41607,7 +41608,7 @@
         <v>44641</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41669,7 +41670,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41726,7 +41727,7 @@
         <v>45121</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41783,7 +41784,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41840,7 +41841,7 @@
         <v>45461</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41897,7 +41898,7 @@
         <v>45237</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41954,7 +41955,7 @@
         <v>45140</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42011,7 +42012,7 @@
         <v>45111</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42068,7 +42069,7 @@
         <v>44767</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42125,7 +42126,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42182,7 +42183,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42239,7 +42240,7 @@
         <v>45230</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42296,7 +42297,7 @@
         <v>44588</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42353,7 +42354,7 @@
         <v>45265</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42410,7 +42411,7 @@
         <v>44803</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42467,7 +42468,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42529,7 +42530,7 @@
         <v>45086</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42586,7 +42587,7 @@
         <v>44075</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42643,7 +42644,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42700,7 +42701,7 @@
         <v>45429</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42757,7 +42758,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42814,7 +42815,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42871,7 +42872,7 @@
         <v>44459</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42928,7 +42929,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42985,7 +42986,7 @@
         <v>44565</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43042,7 +43043,7 @@
         <v>44690</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43099,7 +43100,7 @@
         <v>44768</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43156,7 +43157,7 @@
         <v>44888</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44679</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>44285</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44085</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>44679</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45216</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45595</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>45163</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44487</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>44745</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>45177</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45176</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45712</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>45398</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>45068</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>44479</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>44431</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44848</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>44537</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>44278</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>44679</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45176</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45236</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>45140</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44308</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>44930</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44104</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45217</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>45243</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>44496</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>45293</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45695.55173611111</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>45153</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44088</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44531</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>44597</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>44889</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>44938</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>45294</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44949</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44949</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44082</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44411</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44077</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44228</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44478</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>44238</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>44237</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44201</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>44523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>44077</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44420</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>44608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44510</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>44488</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>44420</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44855</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>44095</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>44573</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44846</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44411</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44496</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44564</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44294</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44405</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44405</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44200</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44776</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44180</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44221</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>44434</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>44466</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44085</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>44419</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>44679</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44679</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>44777</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44111</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>44378</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44256</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44221</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>44222</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>44393</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44350</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>44753</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44445</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44350</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>44510</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>44223</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>44442</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44487</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>44487</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>44469</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>44467</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>44342</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44405</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44823</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>44467</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44515</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>44449</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44767</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>44090</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>44090</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44719</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>44884</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>44487</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44378</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44356</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44152</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>44628</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44253</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>44319</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>44223</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44497</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44378</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44638</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44515</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44882</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44826</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44803</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44525</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44791</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44848</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44074</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44588</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44638</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>44627</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44089</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44785</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>44643</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44116</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44147</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>44595</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44481</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44087</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>44109</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>44574</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>44571</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>44074</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>44393</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>44812</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>44796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>44855</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44110</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>44841</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>44537</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>44809</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45359</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45275</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>45275</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>44090</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44412</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>44501</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44949</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45294</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45341</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45639</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45379</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45222</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45231</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45655.82</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44442</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45208</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45374</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>45219</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45217</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44469</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45275</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45489</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44412</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45111</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>44558</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>44768</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45453</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45268</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44865</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45230</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45483</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>44933</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45785</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>44970</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45316</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44076</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>44509</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45120</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45342</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>44937</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44085</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45271</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44475</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45117</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45483</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>45293</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45140</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45125</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>45116</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>45470</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>44622</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45342</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>44873</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>45155</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45177</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>44929</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45604</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>44099</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>44894</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>44936</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>44931</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>44075</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>44881</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45618</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44130</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>44487</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45610</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45275</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45275</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>44608</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>45804.44638888889</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45625</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>44126.64</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44888</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44084</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44643</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44628</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44803</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44859</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>44600</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>44795</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45741</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44830</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45230</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45071</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>44683</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>45860</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45392</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26736,7 +26736,7 @@
         <v>45712</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45146</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45799</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44944</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45230</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>45202</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45244</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45244</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45827</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45827</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44945</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45244</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44939</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>45140</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>45142</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44936</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44229</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45230</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>45596</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45160</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>44942</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>44909</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45271</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>44690</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45804</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45838</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>45205</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29450,7 +29450,7 @@
         <v>44933</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45089</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>45882.39939814815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>44994</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45166</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44768</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44767</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>44936</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>44967</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>44089</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>44930</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>44865</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45275</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45294</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44888</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45096</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44077</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45614</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45275</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>45729</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>45141</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45887.71827546296</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45225</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>45044</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45142</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44930</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44768</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>45775</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45309</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>45889.68641203704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>45293</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45121</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45894.62824074074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45238</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>44342</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44369</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>45086</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45147</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44293</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44343</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>44767</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44308</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>45244</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>44413</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>44413</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45824</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>45187</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>44180</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>44509</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44824</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44130</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45492</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44958</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44810</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>45013</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45729</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44221</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>45746.70038194444</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>44945</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44151</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44151</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>44949</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>44208</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35337,7 +35337,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>44641</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44916</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45568</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44097</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45111</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>44862</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>45071</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44459</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>45147</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>44454</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45111</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>45492</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>44159</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36730,7 +36730,7 @@
         <v>44565</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>45461</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>44588</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45090</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44740</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44658</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45237</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44123</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44930</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>45082</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45281</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>44812</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>44862</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>45275</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>44180</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>45153</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>45568</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>44104</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>45049</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>45146</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>44665</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>45105</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45236</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>44445</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>44767</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44931</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>44460</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>45302</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45364</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40044,7 +40044,7 @@
         <v>44930</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45245</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>45140</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45308</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40743,7 +40743,7 @@
         <v>45294</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>45217</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>45217</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45429</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>45177</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>45246</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41323,7 +41323,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45623</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45203</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44923</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>44953</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>44302</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45741</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45265</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45219</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45082</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42540,7 +42540,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45300</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43011,7 +43011,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44679</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>44285</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44085</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>44679</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45216</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45595</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>45163</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44487</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>44745</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>45177</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45176</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45712</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>45398</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>45068</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>44479</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>44431</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44848</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>44537</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>44278</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>44679</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45176</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45236</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>45140</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44308</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>44930</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44104</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45217</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>45243</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>44496</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>45293</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45695.55173611111</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>45153</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44088</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44531</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>44597</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>44889</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>44938</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>45294</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44949</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44949</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44082</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44411</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44077</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44228</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44478</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>44238</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>44237</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44201</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>44523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>44077</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44420</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>44608</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44510</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>44488</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>44420</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44855</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>44095</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>44573</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44846</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44411</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44496</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44564</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44294</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44405</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44405</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44200</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44776</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44180</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44221</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>44434</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>44466</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44085</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>44419</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>44679</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44679</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>44777</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44111</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>44378</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44256</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44221</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>44222</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>44393</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44350</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>44753</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44445</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44350</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>44510</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>44223</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>44442</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44487</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>44487</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>44469</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>44467</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>44342</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44405</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44823</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>44467</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44515</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>44449</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44767</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>44090</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>44090</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44719</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>44884</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>44487</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44378</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44356</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44152</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>44628</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44253</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>44319</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>44223</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44497</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>44378</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44638</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44515</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44882</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44826</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44803</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44525</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44791</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44848</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44074</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44588</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44638</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>44627</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44089</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44785</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>44643</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44116</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44147</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>44595</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44481</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44087</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>44109</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>44574</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>44571</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>44074</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>44393</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>44812</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>44796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>44855</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44110</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>44841</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>44537</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>44809</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45359</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45275</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>45275</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>44090</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44412</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>44501</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44949</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45294</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45341</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45639</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45379</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45222</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45231</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45655.82</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44442</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45208</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45374</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>45219</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45217</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44469</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45275</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45489</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44412</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45111</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>44558</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>44768</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45453</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45268</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44865</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>45230</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45483</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>44933</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45785</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>44970</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45316</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44076</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>44509</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45120</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45342</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>44937</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44085</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45271</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44475</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45117</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45483</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>45293</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45140</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45125</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>45116</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>45470</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>44622</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45342</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>44873</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>45155</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45177</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>44929</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45604</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>44099</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>44894</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>44936</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>44931</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>44075</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>44881</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45618</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>44130</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>44487</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45610</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45275</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45275</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>44608</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>45804.44638888889</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45625</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>44126.64</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>44888</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>44084</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44643</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44628</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44803</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44859</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>44600</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>44795</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45741</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44830</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45230</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45071</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>44683</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>45860</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45392</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26736,7 +26736,7 @@
         <v>45712</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45146</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45799</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44944</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45230</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>45202</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45244</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45244</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45827</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45827</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44945</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45244</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44939</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>45140</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>45142</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44936</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44229</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45230</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>45596</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45160</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>44942</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>44909</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45271</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>44690</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45804</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45838</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>45205</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29450,7 +29450,7 @@
         <v>44933</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45089</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>45882.39939814815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>44994</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45166</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44768</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44767</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>44936</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>44967</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>44089</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>44930</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>44865</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45275</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45294</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44888</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45096</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44077</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45614</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45275</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>45729</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>45141</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45887.71827546296</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45225</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>45044</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45142</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44930</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44768</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>45775</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45309</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>45889.68641203704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>45293</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45121</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45894.62824074074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45238</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>44342</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44369</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>45086</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45147</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44293</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44343</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>44767</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44308</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>45244</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>44413</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>44413</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45824</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>45187</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>44180</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>44509</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44824</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44130</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45492</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44958</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44810</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>45013</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45729</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44221</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>45746.70038194444</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>44945</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44151</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44151</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>44949</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>44208</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35337,7 +35337,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>44641</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44916</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44085</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45568</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44097</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45111</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>44862</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>45071</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44459</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>45147</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>44454</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45111</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>45492</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>44159</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36730,7 +36730,7 @@
         <v>44565</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>45461</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>44588</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45090</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44740</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44658</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45237</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44123</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44930</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>45082</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45281</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>44812</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>44862</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>45275</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>44180</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>45153</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>45568</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>44104</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>45049</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>45146</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>44665</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>45105</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45236</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>44445</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>44767</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44931</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>44460</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>45302</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45364</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40044,7 +40044,7 @@
         <v>44930</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>45245</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>45140</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45308</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40743,7 +40743,7 @@
         <v>45294</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>45217</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>45217</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45429</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>45177</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>45246</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41323,7 +41323,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45623</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45203</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44923</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>44953</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>44302</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45741</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45265</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45219</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45082</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42540,7 +42540,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45300</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43011,7 +43011,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44285</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>44679</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>44085</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>44679</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>44745</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45216</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>45398</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45712</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45163</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>44487</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45176</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45068</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45595</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45177</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>44479</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>44431</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44848</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>44537</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>44278</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>44938</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>44679</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>44930</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>45294</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44496</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>45176</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>44088</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>44531</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>45153</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45243</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44949</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44308</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>44597</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45293</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45217</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44104</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44949</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>45140</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44889</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45236</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45695.55173611111</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44082</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44411</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44228</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>44478</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>44238</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>44237</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>44201</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44523</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>44420</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>44608</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44510</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>44488</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>44420</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44855</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>44095</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44573</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>44846</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>44411</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44564</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44496</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44294</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44405</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44405</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44200</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44776</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44180</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>44434</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44221</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>44466</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44085</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>44419</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44679</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>44679</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44777</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44111</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>44378</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44256</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44221</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>44222</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>44393</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44350</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44753</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>44445</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44350</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>44510</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44223</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>44442</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>44487</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44487</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>44467</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>44469</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>44342</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>44405</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44823</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44467</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44515</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>44449</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>44767</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>44090</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44090</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>44719</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44356</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>44628</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>44319</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>44487</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>44253</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44223</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44497</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>44378</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>44638</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>44882</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44515</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>44803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>44525</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>44826</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44791</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>44588</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44089</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>44627</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44638</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44848</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44785</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>44643</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>44595</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>44481</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44116</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>44087</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44109</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44812</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44574</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>44378</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44571</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>44152</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>44796</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>44855</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44110</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45140</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44393</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44939</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44841</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>44537</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>44809</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>44884</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45217</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45217</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>45238</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45294</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>44084</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45625</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45741</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45089</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45231</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44949</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>45142</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45302</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45225</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45785</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45294</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45236</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45219</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>44930</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45268</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>44767</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>45140</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45342</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>44085</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18547,7 +18547,7 @@
         <v>44159</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44293</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>44767</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45316</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44460</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45275</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45275</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45275</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45275</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>44768</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>44658</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45217</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>44208</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44909</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>44930</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>44873</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>45096</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>45071</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45741</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45153</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45309</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44097</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45160</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45271</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>45177</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>45141</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44229</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44123</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44445</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>44454</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44958</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44936</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44085</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45453</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45293</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44894</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45246</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>45245</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44970</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45071</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>45308</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>45120</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>44608</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>44824</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>44865</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44413</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44413</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>44442</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>45090</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>44937</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44343</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45111</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45222</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>44683</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45596</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>45146</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44945</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45077</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
         <v>44888</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>44469</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45827</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44487</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45804</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>44130</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45623</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44949</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>45838</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>45882.39939814815</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44180</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>45614</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45887.71827546296</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45147</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>45775</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45889.68641203704</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>45888</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45013</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>45155</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>45230</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>45121</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>45244</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44558</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45244</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45894.62824074074</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>45824</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>45901.53839120371</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44509</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45341</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>45860</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>44945</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>44302</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>45902.42209490741</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>45483</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>45230</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>45125</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>45610</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>45492</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44865</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>44104</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>45729</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>44740</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>45359</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>44830</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>45082</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>45208</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>45147</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30992,7 +30992,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>44600</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>45202</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45568</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>45568</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>44930</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>45492</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45230</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>44475</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>44151</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>44151</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>44099</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>44953</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32028,7 +32028,7 @@
         <v>45729</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45379</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>45142</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>44130</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44509</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>44881</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>44146</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32779,7 +32779,7 @@
         <v>45281</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44929</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>44933</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>44768</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>44862</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>45203</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33535,7 +33535,7 @@
         <v>44665</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44089</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44126.64</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>44858</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45275</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33944,7 +33944,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45639</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>44936</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>44221</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>45271</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44795</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44628</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>44933</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44942</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>45293</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45082</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>45244</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>45166</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>44412</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44342</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>44931</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>44936</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>44931</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45219</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>44994</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36078,7 +36078,7 @@
         <v>45111</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>45294</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44412</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44923</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36383,7 +36383,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36440,7 +36440,7 @@
         <v>45489</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36497,7 +36497,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44369</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>45205</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44641</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44501</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>45392</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37248,7 +37248,7 @@
         <v>45111</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>44767</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45230</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44588</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45265</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>44944</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>45244</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>45429</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45461</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>45237</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>45140</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44803</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>45086</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>44459</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45746.70038194444</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>45342</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>44565</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45364</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44690</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>45275</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>45275</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>45275</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39325,7 +39325,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44768</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>44888</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44810</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>44967</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>44812</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45177</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>44643</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>45116</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>45146</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40485,7 +40485,7 @@
         <v>45049</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44862</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>45470</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44308</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>45105</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>45618</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44180</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>45187</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41313,7 +41313,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>44930</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>45044</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>44859</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>45712</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>45300</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45655.82</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>44622</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>45604</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45117</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>44090</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45374</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44679</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>44285</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44679</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45595</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45216</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>45163</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44487</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45177</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44745</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45176</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45712</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45398</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45068</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44479</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44431</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44537</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44278</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>44848</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44679</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45236</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>45140</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>45176</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44308</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45148</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>44930</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45243</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>44104</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>45217</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45293</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>44496</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45695.55173611111</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44088</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44597</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44889</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>45153</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>44938</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45294</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44949</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>44949</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>44411</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44228</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44478</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44237</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44238</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44201</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44523</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>44608</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44420</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44510</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44488</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>44420</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>44855</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>44095</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44846</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44411</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>44564</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>44496</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44294</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>44405</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44405</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44573</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44776</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44180</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>44434</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>44466</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>44221</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>44419</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44200</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>44679</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44679</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>44777</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>44111</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>44378</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>44256</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>44221</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44222</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>44393</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44350</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>44753</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44445</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>44350</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44510</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44223</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>44442</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>44487</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44487</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44469</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44467</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>44342</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>44405</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>44823</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44467</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>44515</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>44449</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>44767</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>44090</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>44090</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>44719</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44884</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>44487</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>44628</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>44356</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>44319</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44378</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44253</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44152</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44826</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>44515</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>44791</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>44882</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44525</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44638</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>44803</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>44223</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>44588</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>44627</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>44497</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>44378</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>44638</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>44089</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44785</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>44643</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>44848</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>44087</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>44109</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>44147</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>44595</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44481</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44812</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44574</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44571</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>44796</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>44855</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44110</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>44393</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45222</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>45359</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45275</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45275</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44090</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44841</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>44537</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>44412</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44809</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45379</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>44442</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44501</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44949</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>45294</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45341</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45639</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>45374</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45231</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45655.82</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44469</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45208</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>44116</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45219</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>45217</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>44412</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45275</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45489</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45111</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44768</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44558</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>45453</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45483</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45268</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44865</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>45230</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44509</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44933</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45120</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>44970</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>44937</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45785</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45316</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>45117</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45140</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45125</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45342</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>45271</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>45116</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>44475</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>45470</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45483</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45293</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>44622</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45155</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45342</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45177</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>44873</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>44929</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>44099</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45604</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44894</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>44936</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>44931</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45275</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45275</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>44608</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>44881</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45625</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44130</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>44487</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44643</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45610</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>44803</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>44859</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>44600</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>44795</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>44126.64</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>44888</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>44830</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45230</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>45071</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44628</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>44683</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45741</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44146</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45712</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>45146</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45244</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45230</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45160</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45392</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>44909</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44944</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45230</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45202</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45205</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45827</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45827</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45244</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45244</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44945</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44939</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45140</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45142</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>44936</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>44229</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>45166</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>45596</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44768</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45838</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44942</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>44767</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>45271</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>44858</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>44690</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44089</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44930</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44865</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44933</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45089</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44888</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44994</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45275</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>44936</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44967</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45729</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>45044</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>44930</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>45882.39939814815</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45275</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45294</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45309</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>45096</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>45141</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45225</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45142</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>44768</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>44342</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45293</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>44369</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45086</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45238</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>45147</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44293</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>44343</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44767</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44308</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44413</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>44413</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45187</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44509</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>45244</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44824</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45013</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45729</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45746.70038194444</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>44151</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>44151</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>44916</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45568</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45111</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>44862</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>44454</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45111</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>45492</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44159</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>45077</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>44565</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>44588</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45090</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33316,7 +33316,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>44180</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>44123</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45082</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>44812</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>44862</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45275</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45888</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>44130</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>44180</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>45492</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45614</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>44958</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>45887.71827546296</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>44810</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34756,7 +34756,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>45153</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>45568</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>45775</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>44221</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>44945</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45889.68641203704</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>44949</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>44208</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>44641</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45121</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45894.62824074074</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>44097</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>44459</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45147</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45824</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45461</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44740</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44658</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45901.53839120371</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>45237</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>44930</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45902.42209490741</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45860</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45281</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>45905</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45905</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45905</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44104</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45049</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45146</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44665</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>45105</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>45912.47329861111</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45236</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>44445</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>44767</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>44931</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>45912.47711805555</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45912.4715625</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>44460</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>45302</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45364</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>44930</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39473,7 +39473,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45245</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45140</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45308</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>45294</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45217</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45217</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>45429</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>45177</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>45246</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>45623</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45203</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44923</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>44953</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>44302</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>45741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45265</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41674,7 +41674,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45219</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>45082</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45300</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44679</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>44285</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44679</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45595</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45216</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>45163</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44487</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45177</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44745</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45176</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45712</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45398</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45068</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44479</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44431</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44537</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44278</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>44848</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44679</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45236</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>45140</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>45176</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44308</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45148</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>44930</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45243</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>44104</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>45217</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45293</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>44496</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45695.55173611111</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44088</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44597</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44889</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>45153</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>44938</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45294</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44949</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>44949</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>44411</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44228</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44478</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44237</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44238</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44201</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44523</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>44608</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44420</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44510</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44488</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>44420</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>44855</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>44095</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44846</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44411</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>44564</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>44496</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44294</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>44405</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44405</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44573</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44776</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44180</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>44434</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>44466</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>44221</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>44419</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44200</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>44679</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44679</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>44777</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>44111</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>44378</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>44256</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>44221</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44222</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>44393</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44350</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>44753</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44445</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>44350</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44510</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44223</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>44442</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>44487</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44487</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44469</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44467</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>44342</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>44405</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>44823</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44467</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>44515</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>44449</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>44767</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>44090</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>44090</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>44719</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44884</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>44487</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>44628</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>44356</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>44319</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44378</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44253</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44152</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44826</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>44515</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>44791</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>44882</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44525</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44638</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>44803</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>44223</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>44588</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>44627</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>44497</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>44378</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>44638</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>44089</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44785</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>44643</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>44848</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>44087</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>44109</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>44147</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>44595</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44481</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44812</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44574</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44571</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>44796</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>44855</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44110</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>44393</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45222</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>45359</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45275</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45275</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44090</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44841</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>44537</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>44412</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44809</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45379</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>44442</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44501</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44949</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>45294</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45341</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45639</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>45374</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45231</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45655.82</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44469</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45208</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>44116</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45219</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>45217</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>44412</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45275</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45489</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45111</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44768</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44558</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>45453</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45483</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45268</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44865</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>45230</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44509</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44933</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45120</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>44970</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>44937</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45785</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45316</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>45117</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45140</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45125</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45342</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>45271</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>45116</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>44475</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>45470</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45483</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45293</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>44622</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45155</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45342</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45177</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>44873</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>44929</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>44099</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45604</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44894</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>44936</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>44931</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45275</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45275</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>44608</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>44881</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45625</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44130</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>44487</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44643</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45610</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>44803</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>44859</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>44600</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>44795</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>44126.64</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>44888</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>44830</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45230</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>45071</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44628</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>44683</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45741</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44146</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45712</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>45146</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45244</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45230</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45160</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45392</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>44909</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44944</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45230</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45202</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45205</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>45827</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45827</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45244</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45244</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44945</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44939</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45140</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45142</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>44936</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>44229</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>45166</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>45596</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44768</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45838</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44942</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>44767</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>45271</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>44858</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>44690</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44089</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44930</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44865</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44933</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45089</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44888</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44994</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45275</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>44936</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44967</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45729</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>45044</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>44930</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>45882.39939814815</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45275</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45294</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>45309</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>45096</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>45141</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45225</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45142</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>44768</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>44342</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45293</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>44369</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45086</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45238</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>45147</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44293</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>44343</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44767</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44308</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44413</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>44413</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45187</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44509</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>45244</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44824</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45013</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45729</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45746.70038194444</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>44151</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>44151</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>44916</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45568</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45111</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>44862</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>44454</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45111</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>45492</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44159</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>45077</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>44565</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>44588</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45090</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33316,7 +33316,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>44180</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>44123</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45082</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>44812</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>44862</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45275</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45888</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>44130</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>44180</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>45492</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45614</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>44958</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>45887.71827546296</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>44810</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34756,7 +34756,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>45153</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>45568</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>45775</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>44221</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>44945</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45889.68641203704</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>44949</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>44208</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>44641</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45121</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45894.62824074074</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>44097</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>44459</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45147</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45824</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45461</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>44740</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>44658</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45901.53839120371</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>45237</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>44930</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45902.42209490741</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45860</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45281</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>45905</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45905</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45905</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44104</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45049</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45146</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>44665</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>45105</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>45912.47329861111</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45236</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>44445</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>44767</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>44931</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>45912.47711805555</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45912.4715625</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>44460</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>45302</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45364</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>44930</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39473,7 +39473,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45245</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45140</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45308</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>45294</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45217</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45217</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>45429</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>45177</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>45246</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>45623</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45203</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44923</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>44953</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>44302</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>45741</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45265</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41674,7 +41674,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45219</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>45082</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45300</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44285</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>44679</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44679</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>44745</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>45216</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45398</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45712</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45163</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>44487</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45176</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45068</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45595</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45177</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44431</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44848</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>44479</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>44278</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44679</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44496</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45294</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44938</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>44930</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45176</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44537</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45243</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44949</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44308</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44597</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45217</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>45293</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>44104</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>45148</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45140</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45153</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44949</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44889</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>45236</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45915.44128472222</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45917.71873842592</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>44411</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>44228</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44478</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44238</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44237</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44201</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44523</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>44608</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>44420</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>44510</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44488</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44420</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44855</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44573</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>44846</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>44411</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44564</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44496</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44294</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>44405</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>44405</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>44200</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44776</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>44466</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44180</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44221</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44419</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>44434</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44679</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>44679</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44777</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44111</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>44378</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>44256</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44221</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>44222</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>44393</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>44350</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44753</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>44445</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44350</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44510</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>44223</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>44442</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44487</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>44487</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>44469</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>44467</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>44342</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>44405</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>44823</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44467</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>44515</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>44449</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>44767</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44719</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44378</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44884</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44152</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>44487</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44356</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>44223</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>44628</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44253</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>44319</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>44497</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44378</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44638</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44882</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>44803</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44515</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>44848</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44525</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>44588</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>44627</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>44785</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>44643</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>44147</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>44595</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44116</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>44574</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>44571</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44481</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44393</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44841</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>44537</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44809</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>44826</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>45219</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>44767</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45140</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44791</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>44767</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45294</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45625</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45140</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45741</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>44939</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44638</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45231</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>45217</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>45217</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44949</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>45238</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45785</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>44930</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45268</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>44159</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45342</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>44293</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>45275</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45142</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45302</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45225</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45275</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>45275</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44658</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45217</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44208</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45316</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17880,7 +17880,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44460</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>45483</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45275</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>44109</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>44873</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>44768</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>45096</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45071</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45741</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44812</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>45271</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>45177</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44229</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44123</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44454</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44958</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44936</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>44909</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>44930</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>44796</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>44855</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45453</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45293</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45153</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45309</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44110</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45160</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>45141</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>45245</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>44445</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>44970</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45308</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45120</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>44608</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>44824</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>44894</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45246</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>44865</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>44413</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>44413</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>45090</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45071</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>44937</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45111</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45596</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44945</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>45077</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>45089</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45294</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44442</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45236</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44343</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45222</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>44683</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>44469</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>44130</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45146</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45147</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>44888</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>44487</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>45155</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45623</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45230</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>44949</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>45244</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45244</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>44180</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>44509</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45013</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45341</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>44558</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>44945</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>44302</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45483</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45230</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45125</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45610</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45492</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>44865</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>44104</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>44740</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27916,7 +27916,7 @@
         <v>45729</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45082</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45359</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44830</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>45208</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>45147</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44600</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>45202</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>45568</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45568</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44930</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>45492</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45230</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45729</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>44475</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>44151</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44151</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>44130</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>44953</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>44146</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>45281</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45379</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>45142</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44509</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44881</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44916</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44929</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44933</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44768</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44862</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>45203</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>45827</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>44665</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45827</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>44858</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31163,7 +31163,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>45275</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>44126.64</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>45639</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>44936</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>44221</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>44628</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>45271</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>44795</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>44933</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>44942</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         <v>45293</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>45082</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45244</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>44412</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45166</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>44342</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>44936</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>44931</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>45838</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33183,7 +33183,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>44931</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>45111</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>44412</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>44923</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>45489</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45219</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44994</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44369</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>45614</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45887.71827546296</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>45294</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44501</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>45392</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44944</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>45205</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45775</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>44641</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>45244</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>45889.68641203704</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>45888</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45111</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>45461</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>44767</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45237</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45140</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>45230</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>44588</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>45265</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45121</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>44803</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>45086</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45894.62824074074</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45429</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>44459</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>45901.53839120371</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>44565</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>44690</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>44768</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>44888</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37404,7 +37404,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37575,7 +37575,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>45860</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>45902.42209490741</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37860,7 +37860,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45342</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>44967</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>45177</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>45364</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45905</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45116</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45275</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>45275</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>45275</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>45146</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>45905</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45905</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>44862</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>45470</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39154,7 +39154,7 @@
         <v>44810</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>44308</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45187</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>44812</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>44930</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>44643</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>45044</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>45915.59864583334</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45300</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45912.4715625</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>45912.47329861111</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>45049</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45912.47711805555</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>45655.82</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>44622</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40743,7 +40743,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>45604</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>45917.7152662037</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>45917.72821759259</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45105</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>44180</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
         <v>45117</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>45374</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>44859</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45919</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45712</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45923.56998842592</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45923.5819675926</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45922.85089120371</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>45882.39939814815</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>45824</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>45925.6012962963</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45925.51773148148</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45925.60758101852</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>45924.68075231482</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>44679</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44285</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44679</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45595</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45712</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44745</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>45398</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44487</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44487</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45068</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>45216</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45163</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>45177</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45176</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44848</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44431</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>44537</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44278</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>44479</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>44679</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>44104</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45217</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45915.44128472222</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44496</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45917.71873842592</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>44930</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44938</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45294</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44949</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44949</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44597</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>44889</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45176</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45236</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45140</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>44308</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45148</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45153</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45243</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45293</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44411</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44228</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>44478</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>44237</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44238</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>44201</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>44523</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44608</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44420</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44488</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44420</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>44855</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>44573</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44846</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44411</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>44564</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44496</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44294</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>44405</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44405</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44200</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44776</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44180</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44434</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44466</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>44221</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>44419</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44679</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44679</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44777</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44111</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44378</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>44256</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>44221</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44222</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>44393</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44350</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44753</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>44445</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>44350</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44510</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44223</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44442</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44487</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>44487</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44469</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44467</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44342</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44405</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>44823</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44467</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44515</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>44449</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44767</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44719</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44487</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>44356</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44253</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44882</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44803</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44525</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44588</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44627</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44785</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>44116</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>44643</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44109</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>44147</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44595</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44481</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44812</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>44855</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44110</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>44574</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>44412</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>44571</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>44393</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45222</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>45359</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>45275</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45275</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>44841</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>44537</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>44378</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>44809</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>44826</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45379</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44791</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>44152</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>44884</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44638</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>44223</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44442</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>44628</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>44319</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>44497</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>44378</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44638</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>44515</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45374</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44848</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>44469</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44412</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45392</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>45244</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44944</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44768</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45230</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>45202</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45268</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>44180</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45244</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>44865</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>44945</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45230</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44939</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45901.53839120371</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45902.42209490741</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45140</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45142</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44130</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>45860</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>44933</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45492</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>44958</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>44936</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44810</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>44970</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>44229</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45316</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45905</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45905</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44221</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45596</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44945</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>44949</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45271</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45905</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>44208</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>44641</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>44475</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45293</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>44942</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>45271</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45342</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>44873</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45071</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>44459</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>45147</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45912.47329861111</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>44929</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>44690</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45604</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>44894</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>44936</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>44931</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>44881</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45461</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45912.47711805555</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45912.4715625</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>44740</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>44658</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>44130</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>44933</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>45089</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44487</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45237</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>44930</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45281</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45610</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44994</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45915.59864583334</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45917.7152662037</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44936</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44967</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>44126.64</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44888</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45917.72821759259</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45275</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45294</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44104</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45922.85089120371</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45049</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45096</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>45146</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44665</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45105</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45141</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45225</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45142</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44768</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45919</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>45236</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>44628</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>44445</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44767</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44931</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>45923.5819675926</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45924.68075231482</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45741</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>44146</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45923.56998842592</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44460</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>45302</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44369</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45086</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45147</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44293</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44343</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44767</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44308</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>45364</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44930</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>44413</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>44413</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45245</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>45140</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>45187</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45308</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>45925.60758101852</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45294</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>44475</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45824</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45217</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>45217</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>45429</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44509</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45177</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>45882.39939814815</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45925.6012962963</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44509</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29430,7 +29430,7 @@
         <v>44342</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45925.51773148148</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>44824</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45013</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45729</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29891,7 +29891,7 @@
         <v>45246</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>44151</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>44151</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>45623</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45203</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>44916</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44923</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44953</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>45568</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>44302</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45111</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44862</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45741</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45265</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>44454</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>45219</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45082</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>45492</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>44159</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>45077</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>44565</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>44588</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32263,7 +32263,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45090</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>45300</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>44123</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45082</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45639</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>44812</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45655.82</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45208</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45275</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>44180</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>45153</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>45568</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>45785</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>44501</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>44949</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45294</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>45341</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45342</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>45483</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>45231</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>45219</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45217</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>45275</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45489</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>45111</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35956,7 +35956,7 @@
         <v>44558</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>45453</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>45483</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>44509</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45120</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>44937</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45117</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>45140</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>45125</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45116</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45470</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>44622</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>45155</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>45177</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38018,7 +38018,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45827</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45827</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>45275</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45275</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44608</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>45625</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45838</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>44643</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>44803</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>44859</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>44600</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45614</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>44795</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>45887.71827546296</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40130,7 +40130,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>45775</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         <v>45230</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>45889.68641203704</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45071</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40482,7 +40482,7 @@
         <v>44683</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>45121</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>45894.62824074074</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40943,7 +40943,7 @@
         <v>45712</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45146</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>45244</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41238,7 +41238,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>45230</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41352,7 +41352,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>44909</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45205</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>44768</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44767</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>44858</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>44930</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44865</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44888</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45275</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45729</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45044</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44930</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45309</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45293</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>45238</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>44679</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44285</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44679</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45595</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45712</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44745</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>45398</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44487</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44487</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45068</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>45216</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45163</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>45177</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45176</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44848</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44431</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>44537</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44278</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>44479</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>44679</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>44104</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45217</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45915.44128472222</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44496</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45917.71873842592</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>44930</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44938</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45294</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44949</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44949</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44597</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>44889</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45176</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45236</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45140</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>44308</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45148</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>45737.32148148148</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45153</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45243</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45293</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44411</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44228</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>44478</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>44237</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44238</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>44201</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>44523</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44608</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44420</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44510</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44488</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44420</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>44855</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>44573</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44846</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44411</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>44564</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44496</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44294</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>44405</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44405</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44200</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44776</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44180</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44434</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44466</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>44221</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>44419</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44679</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44679</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44777</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44111</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44378</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>44256</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>44221</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44222</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>44393</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44350</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44753</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>44445</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>44350</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44510</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44223</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>44442</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44487</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>44487</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44469</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44467</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44342</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44405</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>44823</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44467</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44515</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>44449</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44767</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44719</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44487</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>44356</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44253</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44882</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44803</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44525</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44588</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44627</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44785</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>44116</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>44643</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44109</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>44147</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44595</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44481</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44812</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>44855</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44110</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>44574</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45720.62863425926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>44412</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>44571</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>44393</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45222</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>45359</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45275.64769675926</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>45275</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45275</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>44794.57074074074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>44841</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>44537</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45412.70567129629</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>44378</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>44809</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45737.31590277778</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45737.32273148148</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>44826</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45379</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44791</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>44152</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>44884</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44638</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>44223</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44442</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>44628</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>44319</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>44882.57643518518</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>44497</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>44378</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44638</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>44515</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45374</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45268.58987268519</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44848</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>44469</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45755.69678240741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45755.70814814815</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45755.92731481481</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44412</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>45852.91939814815</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>45161.55373842592</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45392</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>45244</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>45852.90648148148</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>45804.67081018518</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45411.46809027778</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44994.36689814815</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45852.93737268518</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45852.9413425926</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45397.42005787037</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44944</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44987.5969212963</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44768</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45230</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44424.61851851852</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>45202</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45229.81049768518</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45268</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>44903.64769675926</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>44180</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45244</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>44865</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45601.47166666666</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45860.56385416666</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>44945</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45555.32940972222</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>44945.8092824074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45230</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44939</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45901.53839120371</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>44909.4740625</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45860.54739583333</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45860.59876157407</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45902.42209490741</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45140</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45142</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44130</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>45860</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>44933</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45492</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>44958</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>44936</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44810</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>44970</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>44229</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45316</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45905</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45905</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44221</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45596</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45320.54717592592</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44945</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>44776.48541666667</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>45576.64189814815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>44949</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45271</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45905</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>44208</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>44911.41037037037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>44641</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>44475</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45293</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>44942</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>44950.64782407408</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>45271</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45342</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>45579.90508101852</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45299.66028935185</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>44483.56151620371</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>44873</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45071</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>44459</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>45147</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45448.4634375</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>44994.48125</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45912.47329861111</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>44929</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>44882.57453703704</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>44690</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>45604</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45294.72739583333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45294.73603009259</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45092.70390046296</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>44894</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>44936</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>44931</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>44227.57215277778</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45111.75905092592</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>44881</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>44475.61988425926</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45461</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>44599.53623842593</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45086.42326388889</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45912.47711805555</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45912.4715625</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>44740</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>44658</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>45624.56611111111</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45607.60791666667</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>44130</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45327.52847222222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>44933</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>45089</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44487</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45237</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>44930</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45281</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45610</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45274.66712962963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44994</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45915.59864583334</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45111.58931712963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45917.7152662037</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45392.60278935185</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45645.66853009259</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44936</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44967</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>44126.64</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44888</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45300.34408564815</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45917.72821759259</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45275</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45294</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44104</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44508.4396412037</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>45153.68471064815</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45922.85089120371</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45049</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45096</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>45146</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44665</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45491.69811342593</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45448.46924768519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45448.47233796296</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45105</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45141</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45597.57811342592</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45225</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45142</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44768</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45919</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>45236</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>44628</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45804.44505787037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>44445</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44767</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44931</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>45923.5819675926</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45924.68075231482</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45475.63047453704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45741</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>44146</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45923.56998842592</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44988.70084490741</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44460</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45579.75803240741</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45555.57263888889</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>45266.54534722222</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>45302</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45082.58068287037</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45750.61050925926</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45590.59991898148</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44369</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45086</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45572.68226851852</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45147</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44293</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44343</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44767</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44308</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>45364</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44431.45556712963</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44930</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>45655.80457175926</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>44413</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>44413</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45245</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>45774.74667824074</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44909.47482638889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28151,7 +28151,7 @@
         <v>45678.56328703704</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>45140</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>45187</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45308</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>45925.60758101852</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45294</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>45491.69741898148</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>44475</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45824</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45217</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>45217</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>45429</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44509</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45177</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>45882.39939814815</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44498.60736111111</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45925.6012962963</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44509</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29430,7 +29430,7 @@
         <v>44342</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45925.51773148148</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45299.67736111111</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>44824</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45774.75024305555</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>45442.63368055555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45013</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45729</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29891,7 +29891,7 @@
         <v>45246</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>44151</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>44151</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>44350.67715277777</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44986.52277777778</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45623.61640046296</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>45623</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45203</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45604.61431712963</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>44916</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44923</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44953</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>45568</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>44302</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>45755.66143518518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>45463.58699074074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45111</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44862</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>45161.37310185185</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>45729.8487037037</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45069.39050925926</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45741</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45265</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>45261.48429398148</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>44454</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45296.51877314815</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>45737.31671296297</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>45219</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>45230.59686342593</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45082</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>45492</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>45268.59717592593</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>44420.49575231481</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>44159</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>45077</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>44565</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>44588</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32263,7 +32263,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>45755.72622685185</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45090</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45655.81387731482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45266.73844907407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>45300</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>44123</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45082</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45695.36659722222</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45639</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>44812</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45655.82</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>45545.65766203704</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45208</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>45671.57730324074</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>45779.37586805555</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45779.39417824074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45555.47070601852</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45275</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>44180</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45491.68972222223</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45491.69962962963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45246.78474537037</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45231.40012731482</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>45153</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>44966.52603009259</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>45568</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>45359.55474537037</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45369.6190162037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>45785</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>44501</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>44949</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45294</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>45341</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45342</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45546.64825231482</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>45664.56349537037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45786.46930555555</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         <v>45573.50582175926</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44546.45023148148</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>45483</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>45231</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45791.37481481482</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>44909.47206018519</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>45219</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45217</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>45195.4384375</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>45593.52091435185</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>45275</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45489.46947916667</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45489</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45337.5977662037</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>45737.64784722222</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>45404.48288194444</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>45111</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>45793.47493055555</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35956,7 +35956,7 @@
         <v>44558</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>45275.35924768518</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>45453</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>45483</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>45106.46225694445</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45106.46359953703</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45106.46465277778</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>45456.67717592593</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>45573.49461805556</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>45804.65851851852</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45804.66534722222</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>44509</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45037.55094907407</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45120</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>44937</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45030.5583912037</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45644.6893287037</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45117</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>45750.62740740741</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>45140</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>45125</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45316.35028935185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45812.4794212963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45678.54631944445</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45116</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45470</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>45579.69619212963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>44622</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45818.4428125</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>45155</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>44993.24648148148</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45817.52960648148</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>45177</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45816.80521990741</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45816.81532407407</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45818.45112268518</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38018,7 +38018,7 @@
         <v>45818.4477662037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45819.34208333334</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45819.35346064815</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>45821.4375462963</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>45824.6057175926</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>45824.6219212963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45825.41101851852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45827</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45827</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45005.58341435185</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45274.94810185185</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>45275</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45275</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>45541.59120370371</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44608</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45833.6840162037</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>45833.68815972222</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>45625</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45838</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>44643</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>45842.65444444444</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>45727.41893518518</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45601.53907407408</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>44803</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>44859</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45655.79679398148</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45888</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>44600</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45614</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>44795</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>45737.31425925926</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45737.3153125</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>45737.32219907407</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>45887.71827546296</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40130,7 +40130,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>45775</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>44830</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         <v>45230</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>45889.68641203704</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45071</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40482,7 +40482,7 @@
         <v>44683</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45655.81140046296</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>45121</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>45204.62655092592</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>45894.62824074074</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>44638.21601851852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44623.6377199074</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45703.67853009259</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40943,7 +40943,7 @@
         <v>45712</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45146</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>45111.58732638889</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>45774.74922453704</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41176,7 +41176,7 @@
         <v>45244</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41238,7 +41238,7 @@
         <v>45231.39583333334</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>45230</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41352,7 +41352,7 @@
         <v>45160</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>44909</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>44743.53112268518</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45205</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45735.53318287037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>44909.47087962963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45166</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45306.82501157407</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>44768</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44767</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>44858</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>44775.39832175926</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>44930</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44865</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>44888</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45275</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45729</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45153.5702662037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45044</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44930</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45309</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45293</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>45238</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>45048.54754629629</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>

--- a/Översikt LINKÖPING.xlsx
+++ b/Översikt LINKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45756</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>44679</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>45644.42954861111</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45355</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45860.61114583333</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45720.62849537037</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44293</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>44180</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>44421</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44479</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44679</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>45714.45943287037</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44285</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>45555.53145833333</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45621.71255787037</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45932</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>45664.56525462963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45756.55734953703</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>44679</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44405.38357638889</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>45163</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44745</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>45216</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45176</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44487</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>44487</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>45177</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>45621.7202662037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>45068</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45595</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>45398</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>45712</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45727.44623842592</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45782.35407407407</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45774.7449537037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>45774.74971064815</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45816.7908912037</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45804.64479166667</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>44405.37199074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44848</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44431</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>44537</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44479</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>44278</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44679</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45757.43452546297</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45665.88498842593</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44938</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>44930</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>45191.74868055555</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>45915.44128472222</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>44597</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45217</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>45917.71873842592</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45293</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>45554.7571875</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>45148</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45266.73542824074</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>44949</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45745.45288194445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>45140</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>44298.96792824074</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>45774.74846064814</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>45786.78096064815</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>44889</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>45554.724375</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44496</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45932</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45236</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>45932</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45243</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>45176</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>45294</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>45812.72518518518</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>45153</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44949</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44308</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44411.46893518518</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44411</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44228</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44478</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>44238</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>44237</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>44201</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>44608</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44420</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44510</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44488</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44764.75119212963</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44420</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44855</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44573</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44846</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44411</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44564</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>44496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44294</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44782.48431712963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44853.62758101852</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44405</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>44405</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44200</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44776</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44180</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>44466</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>44434</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44221</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44419</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44777</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44679</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44679</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44111</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44378</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44256</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44221</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44222</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44393</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>44455.59368055555</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44350</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>44753</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44445</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44347.39319444444</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44293.54331018519</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44382.29873842592</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44350</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>44510</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>44223</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44442</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44487</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>44487</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44469</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44467</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44342</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>44201.57689814815</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>44405</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44823</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>44467</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44515</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>44449</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44767</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>44719</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>44487</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>44356</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44776.43607638889</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44692.5827662037</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>44882</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>44803</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>44253</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>44627</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44588</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>44785</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>44116</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>44643</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>44109</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44446.44587962963</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>44382.29295138889</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>44720.78243055556</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44595</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44481</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44371.45949074074</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>44743.39017361111</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>44308.73248842593</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44743.53200231482</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>44812</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44776.49267361111</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>44147</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         <v>44855</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44277.45946759259</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>44110</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44227.57533564815</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>44498.63189814815</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44574</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>44945.79784722222</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45728.64946759259</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44794.57594907407</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>45274.66761574074</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>44571</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>44378</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>45477.43600694444</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>44309.38962962963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45089</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44152</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45448.46712962963</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>44393</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>44826</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45435.65314814815</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45294</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44791</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44223</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45236</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44405.3794212963</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>45268.5847337963</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>45457.59011574074</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>44498.62533564815</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>44498.6764699074</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44638</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44497</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44378</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>44638</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45219</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>44767</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>44841</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>44537</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>44809</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>44848</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>45140</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>44767</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>44884</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         <v>44884.59502314815</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45492</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>44865</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45729</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44628</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>44319</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>44930</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>45485.6846412037</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45359</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>44897.58119212963</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>44830</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45140</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45579.7454050926</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45748.55282407408</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>45748.56105324074</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45208</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>45492</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>45230</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>44939</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>44475</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>44151</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45147</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>44151</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44515</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>44986.54665509259</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44953</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>44600</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>45202</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>44525</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>44525.62849537037</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>45448.46574074074</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45379</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>45217</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45217</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45092.70306712963</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45142</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>45300.3408912037</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>45182.38091435185</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>44509</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45238</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45225.27888888889</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45225.27950231481</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45704.41174768518</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>44881</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>45915.59864583334</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45152.45078703704</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45912.4715625</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45209.38177083333</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45729</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45912.47329861111</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45021.41194444444</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45912.47711805555</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44130</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45547.66443287037</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45604.6397337963</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44146</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>45281</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>44858</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>44783.43192129629</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>45275</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45460.46664351852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45623.61754629629</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45142</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>45638.66378472222</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>45639.31511574074</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>45639</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45302</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45225</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>44221</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>44916</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45427.39541666667</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45875.37489583333</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45917.7152662037</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45917.72821759259</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44628</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>44929</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45774.74288194445</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45774.74611111111</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>44928.80907407407</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>44933</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>44965.61106481482</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>44986.55711805556</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>44768</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44909.47282407407</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>44862</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>44889.59107638889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45203</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44944.35847222222</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45316.34875</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>45316</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44460</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>44665</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>44498.63928240741</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44498.66814814815</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>45655.83563657408</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45655.84232638889</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>45275</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44860.31635416667</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45133.94640046296</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>44354.65108796296</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45166</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44126.64<